--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124801891</v>
+        <v>124805236</v>
       </c>
       <c r="B2" t="n">
-        <v>78891</v>
+        <v>77743</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437896</v>
+        <v>437817</v>
       </c>
       <c r="R2" t="n">
-        <v>7028421</v>
+        <v>7028282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124806977</v>
+        <v>124802526</v>
       </c>
       <c r="B3" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,26 +808,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,24 +835,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437826</v>
+        <v>437884</v>
       </c>
       <c r="R3" t="n">
-        <v>7028421</v>
+        <v>7028332</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802109</v>
+        <v>124807783</v>
       </c>
       <c r="B4" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,41 +930,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437857</v>
+        <v>437870</v>
       </c>
       <c r="R4" t="n">
-        <v>7028393</v>
+        <v>7028581</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802330</v>
+        <v>124806928</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,13 +1084,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437866</v>
+        <v>437831</v>
       </c>
       <c r="R5" t="n">
-        <v>7028363</v>
+        <v>7028417</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807390</v>
+        <v>124802109</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,25 +1173,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437771</v>
+        <v>437857</v>
       </c>
       <c r="R6" t="n">
-        <v>7028497</v>
+        <v>7028393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802848</v>
+        <v>124801857</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,21 +1294,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1328,13 +1318,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437865</v>
+        <v>437882</v>
       </c>
       <c r="R7" t="n">
-        <v>7028297</v>
+        <v>7028436</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,12 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802211</v>
+        <v>124802608</v>
       </c>
       <c r="B8" t="n">
-        <v>79919</v>
+        <v>79927</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,21 +1411,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437849</v>
+        <v>437883</v>
       </c>
       <c r="R8" t="n">
-        <v>7028377</v>
+        <v>7028325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,12 +1480,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802182</v>
+        <v>124801717</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,43 +1528,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437853</v>
+        <v>437880</v>
       </c>
       <c r="R9" t="n">
-        <v>7028377</v>
+        <v>7028440</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,12 +1597,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802943</v>
+        <v>124802211</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,50 +1641,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437861</v>
+        <v>437849</v>
       </c>
       <c r="R10" t="n">
-        <v>7028295</v>
+        <v>7028377</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,12 +1714,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124801857</v>
+        <v>124806762</v>
       </c>
       <c r="B11" t="n">
-        <v>77743</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,21 +1762,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1814,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437882</v>
+        <v>437830</v>
       </c>
       <c r="R11" t="n">
-        <v>7028436</v>
+        <v>7028451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1821,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,12 +1831,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,10 +1863,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805236</v>
+        <v>124806977</v>
       </c>
       <c r="B12" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,34 +1879,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437817</v>
+        <v>437826</v>
       </c>
       <c r="R12" t="n">
-        <v>7028282</v>
+        <v>7028421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,7 +1952,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,12 +1962,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2008,10 +1994,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802466</v>
+        <v>124804979</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,37 +2010,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437886</v>
+        <v>437811</v>
       </c>
       <c r="R13" t="n">
-        <v>7028342</v>
+        <v>7028294</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,7 +2078,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,12 +2088,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,10 +2120,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802401</v>
+        <v>124802943</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,37 +2136,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437856</v>
+        <v>437861</v>
       </c>
       <c r="R14" t="n">
-        <v>7028363</v>
+        <v>7028295</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2210,12 +2214,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,10 +2246,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806762</v>
+        <v>124801643</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2258,37 +2262,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437830</v>
+        <v>437865</v>
       </c>
       <c r="R15" t="n">
-        <v>7028451</v>
+        <v>7028458</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2317,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2327,12 +2340,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,7 +2372,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124801717</v>
+        <v>124802342</v>
       </c>
       <c r="B16" t="n">
         <v>74901</v>
@@ -2399,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437880</v>
+        <v>437861</v>
       </c>
       <c r="R16" t="n">
-        <v>7028440</v>
+        <v>7028347</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2434,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2444,12 +2457,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2476,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807432</v>
+        <v>124807102</v>
       </c>
       <c r="B17" t="n">
-        <v>78891</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,46 +2505,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437768</v>
+        <v>437750</v>
       </c>
       <c r="R17" t="n">
-        <v>7028490</v>
+        <v>7028464</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2560,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2570,12 +2574,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804979</v>
+        <v>124802848</v>
       </c>
       <c r="B18" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,46 +2622,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437811</v>
+        <v>437865</v>
       </c>
       <c r="R18" t="n">
-        <v>7028294</v>
+        <v>7028297</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2696,12 +2691,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124802526</v>
+        <v>124802401</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2744,46 +2739,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437884</v>
+        <v>437856</v>
       </c>
       <c r="R19" t="n">
-        <v>7028332</v>
+        <v>7028363</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2812,7 +2798,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2822,12 +2808,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,10 +2840,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802067</v>
+        <v>124802466</v>
       </c>
       <c r="B20" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2866,25 +2852,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2894,13 +2880,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437900</v>
+        <v>437886</v>
       </c>
       <c r="R20" t="n">
-        <v>7028398</v>
+        <v>7028342</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2929,7 +2915,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2939,12 +2925,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124807102</v>
+        <v>124804958</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2987,37 +2973,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437750</v>
+        <v>437804</v>
       </c>
       <c r="R21" t="n">
-        <v>7028464</v>
+        <v>7028292</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3046,7 +3037,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3056,12 +3047,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3088,10 +3079,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802342</v>
+        <v>124806603</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,41 +3091,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437861</v>
+        <v>437790</v>
       </c>
       <c r="R22" t="n">
-        <v>7028347</v>
+        <v>7028422</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3163,7 +3168,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3173,12 +3178,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,10 +3210,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802608</v>
+        <v>124805246</v>
       </c>
       <c r="B23" t="n">
-        <v>79927</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3217,25 +3222,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3245,10 +3250,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437883</v>
+        <v>437817</v>
       </c>
       <c r="R23" t="n">
-        <v>7028325</v>
+        <v>7028282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3280,7 +3285,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3290,12 +3295,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3322,10 +3327,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806329</v>
+        <v>124807390</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,21 +3343,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,13 +3367,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437744</v>
+        <v>437771</v>
       </c>
       <c r="R24" t="n">
-        <v>7028312</v>
+        <v>7028497</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3397,7 +3402,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3407,12 +3412,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3439,10 +3444,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124806603</v>
+        <v>124807162</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>77753</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3451,55 +3456,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437790</v>
+        <v>437731</v>
       </c>
       <c r="R25" t="n">
-        <v>7028422</v>
+        <v>7028449</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3528,7 +3519,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3538,12 +3529,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3570,10 +3561,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124805246</v>
+        <v>124802330</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,21 +3577,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3610,13 +3601,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437817</v>
+        <v>437866</v>
       </c>
       <c r="R26" t="n">
-        <v>7028282</v>
+        <v>7028363</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3645,7 +3636,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3655,12 +3646,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3687,7 +3678,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124801643</v>
+        <v>124802182</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3722,7 +3713,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3736,13 +3727,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437865</v>
+        <v>437853</v>
       </c>
       <c r="R27" t="n">
-        <v>7028458</v>
+        <v>7028377</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3771,7 +3762,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3781,12 +3772,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124806928</v>
+        <v>124806329</v>
       </c>
       <c r="B28" t="n">
-        <v>79920</v>
+        <v>78891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3825,25 +3816,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3853,13 +3844,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437831</v>
+        <v>437744</v>
       </c>
       <c r="R28" t="n">
-        <v>7028417</v>
+        <v>7028312</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3888,7 +3879,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,12 +3889,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124807783</v>
+        <v>124801891</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3946,26 +3937,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3973,19 +3964,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437870</v>
+        <v>437896</v>
       </c>
       <c r="R29" t="n">
-        <v>7028581</v>
+        <v>7028421</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4014,7 +4010,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4024,12 +4020,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4056,10 +4052,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124804958</v>
+        <v>124802067</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>74885</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4068,46 +4064,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437804</v>
+        <v>437900</v>
       </c>
       <c r="R30" t="n">
-        <v>7028292</v>
+        <v>7028398</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4127,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4137,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4169,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124807162</v>
+        <v>124807432</v>
       </c>
       <c r="B31" t="n">
-        <v>77753</v>
+        <v>78891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4194,34 +4185,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437731</v>
+        <v>437768</v>
       </c>
       <c r="R31" t="n">
-        <v>7028449</v>
+        <v>7028490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124805236</v>
+        <v>124802848</v>
       </c>
       <c r="B2" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437817</v>
+        <v>437865</v>
       </c>
       <c r="R2" t="n">
-        <v>7028282</v>
+        <v>7028297</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802526</v>
+        <v>124807390</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,46 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437884</v>
+        <v>437771</v>
       </c>
       <c r="R3" t="n">
-        <v>7028332</v>
+        <v>7028497</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124807783</v>
+        <v>124802342</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,46 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437870</v>
+        <v>437861</v>
       </c>
       <c r="R4" t="n">
-        <v>7028581</v>
+        <v>7028347</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124806928</v>
+        <v>124801857</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>77743</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437831</v>
+        <v>437882</v>
       </c>
       <c r="R5" t="n">
-        <v>7028417</v>
+        <v>7028436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802109</v>
+        <v>124805236</v>
       </c>
       <c r="B6" t="n">
-        <v>96227</v>
+        <v>77743</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437857</v>
+        <v>437817</v>
       </c>
       <c r="R6" t="n">
-        <v>7028393</v>
+        <v>7028282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124801857</v>
+        <v>124802211</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>79919</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,25 +1272,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437882</v>
+        <v>437849</v>
       </c>
       <c r="R7" t="n">
-        <v>7028436</v>
+        <v>7028377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802608</v>
+        <v>124804958</v>
       </c>
       <c r="B8" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,41 +1389,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437883</v>
+        <v>437804</v>
       </c>
       <c r="R8" t="n">
-        <v>7028325</v>
+        <v>7028292</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,12 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124801717</v>
+        <v>124802109</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,25 +1511,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437880</v>
+        <v>437857</v>
       </c>
       <c r="R9" t="n">
-        <v>7028440</v>
+        <v>7028393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802211</v>
+        <v>124802330</v>
       </c>
       <c r="B10" t="n">
-        <v>79919</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,13 +1656,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437849</v>
+        <v>437866</v>
       </c>
       <c r="R10" t="n">
-        <v>7028377</v>
+        <v>7028363</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,12 +1701,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124806762</v>
+        <v>124802067</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>74885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1745,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437830</v>
+        <v>437900</v>
       </c>
       <c r="R11" t="n">
-        <v>7028451</v>
+        <v>7028398</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,12 +1818,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124806977</v>
+        <v>124802526</v>
       </c>
       <c r="B12" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,26 +1866,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1906,24 +1893,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437826</v>
+        <v>437884</v>
       </c>
       <c r="R12" t="n">
-        <v>7028421</v>
+        <v>7028332</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1952,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1962,12 +1944,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804979</v>
+        <v>124802466</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,46 +1992,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437811</v>
+        <v>437886</v>
       </c>
       <c r="R13" t="n">
-        <v>7028294</v>
+        <v>7028342</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2078,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2088,12 +2061,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2120,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802943</v>
+        <v>124801717</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,46 +2109,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437861</v>
+        <v>437880</v>
       </c>
       <c r="R14" t="n">
-        <v>7028295</v>
+        <v>7028440</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2204,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2214,12 +2178,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2246,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124801643</v>
+        <v>124804979</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2262,31 +2226,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2295,13 +2259,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437865</v>
+        <v>437811</v>
       </c>
       <c r="R15" t="n">
-        <v>7028458</v>
+        <v>7028294</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,7 +2294,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2340,12 +2304,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,10 +2336,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802342</v>
+        <v>124802943</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,24 +2352,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
@@ -2415,10 +2388,10 @@
         <v>437861</v>
       </c>
       <c r="R16" t="n">
-        <v>7028347</v>
+        <v>7028295</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,12 +2430,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807102</v>
+        <v>124806928</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>79920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,25 +2474,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2529,13 +2502,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437750</v>
+        <v>437831</v>
       </c>
       <c r="R17" t="n">
-        <v>7028464</v>
+        <v>7028417</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2564,7 +2537,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2574,12 +2547,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802848</v>
+        <v>124807162</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>77753</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2646,13 +2619,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437865</v>
+        <v>437731</v>
       </c>
       <c r="R18" t="n">
-        <v>7028297</v>
+        <v>7028449</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,7 +2654,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,12 +2664,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,10 +2696,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124802401</v>
+        <v>124806762</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,21 +2712,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2763,10 +2736,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437856</v>
+        <v>437830</v>
       </c>
       <c r="R19" t="n">
-        <v>7028363</v>
+        <v>7028451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2798,7 +2771,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2808,12 +2781,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2840,10 +2813,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802466</v>
+        <v>124801891</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,37 +2829,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437886</v>
+        <v>437896</v>
       </c>
       <c r="R20" t="n">
-        <v>7028342</v>
+        <v>7028421</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2915,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2925,12 +2912,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,10 +2944,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804958</v>
+        <v>124806603</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,31 +2956,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3002,13 +2998,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437804</v>
+        <v>437790</v>
       </c>
       <c r="R21" t="n">
-        <v>7028292</v>
+        <v>7028422</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3037,7 +3033,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3047,12 +3043,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3079,10 +3075,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806603</v>
+        <v>124807102</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,55 +3087,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437790</v>
+        <v>437750</v>
       </c>
       <c r="R22" t="n">
-        <v>7028422</v>
+        <v>7028464</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3168,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3178,12 +3160,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,10 +3192,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124805246</v>
+        <v>124801643</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3226,37 +3208,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437817</v>
+        <v>437865</v>
       </c>
       <c r="R23" t="n">
-        <v>7028282</v>
+        <v>7028458</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3285,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3295,12 +3286,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3327,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124807390</v>
+        <v>124802401</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3343,21 +3334,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3367,10 +3358,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437771</v>
+        <v>437856</v>
       </c>
       <c r="R24" t="n">
-        <v>7028497</v>
+        <v>7028363</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3402,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3412,12 +3403,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,10 +3435,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124807162</v>
+        <v>124807783</v>
       </c>
       <c r="B25" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3460,37 +3451,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437731</v>
+        <v>437870</v>
       </c>
       <c r="R25" t="n">
-        <v>7028449</v>
+        <v>7028581</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3561,10 +3561,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802330</v>
+        <v>124807432</v>
       </c>
       <c r="B26" t="n">
-        <v>88359</v>
+        <v>78891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3577,37 +3577,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437866</v>
+        <v>437768</v>
       </c>
       <c r="R26" t="n">
-        <v>7028363</v>
+        <v>7028490</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3636,7 +3645,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3646,12 +3655,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3678,10 +3687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802182</v>
+        <v>124805246</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3694,43 +3703,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437853</v>
+        <v>437817</v>
       </c>
       <c r="R27" t="n">
-        <v>7028377</v>
+        <v>7028282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3804,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124806329</v>
+        <v>124802182</v>
       </c>
       <c r="B28" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3820,37 +3820,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437744</v>
+        <v>437853</v>
       </c>
       <c r="R28" t="n">
-        <v>7028312</v>
+        <v>7028377</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3879,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3889,12 +3898,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3921,7 +3930,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124801891</v>
+        <v>124806977</v>
       </c>
       <c r="B29" t="n">
         <v>78891</v>
@@ -3956,7 +3965,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3975,7 +3984,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437896</v>
+        <v>437826</v>
       </c>
       <c r="R29" t="n">
         <v>7028421</v>
@@ -4010,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4020,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4052,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124802067</v>
+        <v>124806329</v>
       </c>
       <c r="B30" t="n">
-        <v>74885</v>
+        <v>78891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4064,25 +4073,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4092,13 +4101,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437900</v>
+        <v>437744</v>
       </c>
       <c r="R30" t="n">
-        <v>7028398</v>
+        <v>7028312</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4127,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4137,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4169,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124807432</v>
+        <v>124802608</v>
       </c>
       <c r="B31" t="n">
-        <v>78891</v>
+        <v>79927</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4181,47 +4190,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437768</v>
+        <v>437883</v>
       </c>
       <c r="R31" t="n">
-        <v>7028490</v>
+        <v>7028325</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804958</v>
+        <v>124802109</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,46 +1389,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437804</v>
+        <v>437857</v>
       </c>
       <c r="R8" t="n">
-        <v>7028292</v>
+        <v>7028393</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802109</v>
+        <v>124802330</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1539,13 +1534,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437857</v>
+        <v>437866</v>
       </c>
       <c r="R9" t="n">
-        <v>7028393</v>
+        <v>7028363</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802330</v>
+        <v>124804958</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,37 +1627,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437866</v>
+        <v>437804</v>
       </c>
       <c r="R10" t="n">
-        <v>7028363</v>
+        <v>7028292</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807162</v>
+        <v>124806762</v>
       </c>
       <c r="B18" t="n">
-        <v>77753</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437731</v>
+        <v>437830</v>
       </c>
       <c r="R18" t="n">
-        <v>7028449</v>
+        <v>7028451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806762</v>
+        <v>124807162</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>77753</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437830</v>
+        <v>437731</v>
       </c>
       <c r="R19" t="n">
-        <v>7028451</v>
+        <v>7028449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802109</v>
+        <v>124804958</v>
       </c>
       <c r="B8" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,41 +1389,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437857</v>
+        <v>437804</v>
       </c>
       <c r="R8" t="n">
-        <v>7028393</v>
+        <v>7028292</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802330</v>
+        <v>124802109</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1511,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437866</v>
+        <v>437857</v>
       </c>
       <c r="R9" t="n">
-        <v>7028363</v>
+        <v>7028393</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804958</v>
+        <v>124802330</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,42 +1632,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437804</v>
+        <v>437866</v>
       </c>
       <c r="R10" t="n">
-        <v>7028292</v>
+        <v>7028363</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124806762</v>
+        <v>124807162</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>77753</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437830</v>
+        <v>437731</v>
       </c>
       <c r="R18" t="n">
-        <v>7028451</v>
+        <v>7028449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124807162</v>
+        <v>124806762</v>
       </c>
       <c r="B19" t="n">
-        <v>77753</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437731</v>
+        <v>437830</v>
       </c>
       <c r="R19" t="n">
-        <v>7028449</v>
+        <v>7028451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802848</v>
+        <v>124802109</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437865</v>
+        <v>437857</v>
       </c>
       <c r="R2" t="n">
-        <v>7028297</v>
+        <v>7028393</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124807390</v>
+        <v>124804958</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437771</v>
+        <v>437804</v>
       </c>
       <c r="R3" t="n">
-        <v>7028497</v>
+        <v>7028292</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802342</v>
+        <v>124806603</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +926,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437861</v>
+        <v>437790</v>
       </c>
       <c r="R4" t="n">
-        <v>7028347</v>
+        <v>7028422</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124801857</v>
+        <v>124805236</v>
       </c>
       <c r="B5" t="n">
         <v>77743</v>
@@ -1066,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437882</v>
+        <v>437817</v>
       </c>
       <c r="R5" t="n">
-        <v>7028436</v>
+        <v>7028282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805236</v>
+        <v>124806977</v>
       </c>
       <c r="B6" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1178,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437817</v>
+        <v>437826</v>
       </c>
       <c r="R6" t="n">
-        <v>7028282</v>
+        <v>7028421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1261,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802211</v>
+        <v>124801857</v>
       </c>
       <c r="B7" t="n">
-        <v>79919</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1305,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437849</v>
+        <v>437882</v>
       </c>
       <c r="R7" t="n">
-        <v>7028377</v>
+        <v>7028436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1368,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1378,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804958</v>
+        <v>124802848</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,42 +1426,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437804</v>
+        <v>437865</v>
       </c>
       <c r="R8" t="n">
-        <v>7028292</v>
+        <v>7028297</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,12 +1495,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802109</v>
+        <v>124802943</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,41 +1539,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437857</v>
+        <v>437861</v>
       </c>
       <c r="R9" t="n">
-        <v>7028393</v>
+        <v>7028295</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1611,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1621,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802330</v>
+        <v>124807432</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>78891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,37 +1669,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437866</v>
+        <v>437768</v>
       </c>
       <c r="R10" t="n">
-        <v>7028363</v>
+        <v>7028490</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,7 +1737,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,12 +1747,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802067</v>
+        <v>124801643</v>
       </c>
       <c r="B11" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,41 +1791,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437900</v>
+        <v>437865</v>
       </c>
       <c r="R11" t="n">
-        <v>7028398</v>
+        <v>7028458</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802526</v>
+        <v>124805246</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,46 +1921,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437884</v>
+        <v>437817</v>
       </c>
       <c r="R12" t="n">
-        <v>7028332</v>
+        <v>7028282</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1934,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,12 +1990,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2210,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804979</v>
+        <v>124802182</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,31 +2272,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2259,13 +2305,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437811</v>
+        <v>437853</v>
       </c>
       <c r="R15" t="n">
-        <v>7028294</v>
+        <v>7028377</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2294,7 +2340,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2304,12 +2350,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,10 +2382,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802943</v>
+        <v>124802067</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>74885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,50 +2394,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437861</v>
+        <v>437900</v>
       </c>
       <c r="R16" t="n">
-        <v>7028295</v>
+        <v>7028398</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2420,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806928</v>
+        <v>124806762</v>
       </c>
       <c r="B17" t="n">
-        <v>79920</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,25 +2511,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2502,10 +2539,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437831</v>
+        <v>437830</v>
       </c>
       <c r="R17" t="n">
-        <v>7028417</v>
+        <v>7028451</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2537,7 +2574,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2547,12 +2584,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807162</v>
+        <v>124802608</v>
       </c>
       <c r="B18" t="n">
-        <v>77753</v>
+        <v>79927</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>314</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437731</v>
+        <v>437883</v>
       </c>
       <c r="R18" t="n">
-        <v>7028449</v>
+        <v>7028325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,7 +2691,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2664,12 +2701,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2733,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806762</v>
+        <v>124804979</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,37 +2749,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437830</v>
+        <v>437811</v>
       </c>
       <c r="R19" t="n">
-        <v>7028451</v>
+        <v>7028294</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2771,7 +2817,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2781,12 +2827,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124801891</v>
+        <v>124802211</v>
       </c>
       <c r="B20" t="n">
-        <v>78891</v>
+        <v>79919</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2825,52 +2871,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437896</v>
+        <v>437849</v>
       </c>
       <c r="R20" t="n">
-        <v>7028421</v>
+        <v>7028377</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2902,7 +2934,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,12 +2944,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124806603</v>
+        <v>124802526</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2956,40 +2988,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2998,10 +3025,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437790</v>
+        <v>437884</v>
       </c>
       <c r="R21" t="n">
-        <v>7028422</v>
+        <v>7028332</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -3033,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3043,12 +3070,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,10 +3102,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124807102</v>
+        <v>124807783</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,37 +3118,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437750</v>
+        <v>437870</v>
       </c>
       <c r="R22" t="n">
-        <v>7028464</v>
+        <v>7028581</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3150,7 +3186,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,12 +3196,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3192,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124801643</v>
+        <v>124807102</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3208,43 +3244,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437865</v>
+        <v>437750</v>
       </c>
       <c r="R23" t="n">
-        <v>7028458</v>
+        <v>7028464</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3276,7 +3303,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,12 +3313,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3435,10 +3462,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124807783</v>
+        <v>124806928</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,50 +3474,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437870</v>
+        <v>437831</v>
       </c>
       <c r="R25" t="n">
-        <v>7028581</v>
+        <v>7028417</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3519,7 +3537,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3529,12 +3547,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3561,10 +3579,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124807432</v>
+        <v>124802342</v>
       </c>
       <c r="B26" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3577,43 +3595,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437768</v>
+        <v>437861</v>
       </c>
       <c r="R26" t="n">
-        <v>7028490</v>
+        <v>7028347</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3645,7 +3654,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3655,12 +3664,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3687,10 +3696,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124805246</v>
+        <v>124802330</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3703,21 +3712,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3727,13 +3736,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437817</v>
+        <v>437866</v>
       </c>
       <c r="R27" t="n">
-        <v>7028282</v>
+        <v>7028363</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3762,7 +3771,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3772,12 +3781,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3804,10 +3813,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802182</v>
+        <v>124806329</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3820,46 +3829,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437853</v>
+        <v>437744</v>
       </c>
       <c r="R28" t="n">
-        <v>7028377</v>
+        <v>7028312</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124806977</v>
+        <v>124801891</v>
       </c>
       <c r="B29" t="n">
         <v>78891</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437826</v>
+        <v>437896</v>
       </c>
       <c r="R29" t="n">
         <v>7028421</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124806329</v>
+        <v>124807390</v>
       </c>
       <c r="B30" t="n">
-        <v>78891</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4077,21 +4077,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437744</v>
+        <v>437771</v>
       </c>
       <c r="R30" t="n">
-        <v>7028312</v>
+        <v>7028497</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124802608</v>
+        <v>124807162</v>
       </c>
       <c r="B31" t="n">
-        <v>79927</v>
+        <v>77753</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4190,25 +4190,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437883</v>
+        <v>437731</v>
       </c>
       <c r="R31" t="n">
-        <v>7028325</v>
+        <v>7028449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124804958</v>
+        <v>124802466</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437804</v>
+        <v>437886</v>
       </c>
       <c r="R3" t="n">
-        <v>7028292</v>
+        <v>7028342</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124806603</v>
+        <v>124802401</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,55 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437790</v>
+        <v>437856</v>
       </c>
       <c r="R4" t="n">
-        <v>7028422</v>
+        <v>7028363</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805236</v>
+        <v>124807162</v>
       </c>
       <c r="B5" t="n">
-        <v>77743</v>
+        <v>77753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437817</v>
+        <v>437731</v>
       </c>
       <c r="R5" t="n">
-        <v>7028282</v>
+        <v>7028449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124806977</v>
+        <v>124807432</v>
       </c>
       <c r="B6" t="n">
         <v>78891</v>
@@ -1197,7 +1178,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1205,21 +1186,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437826</v>
+        <v>437768</v>
       </c>
       <c r="R6" t="n">
-        <v>7028421</v>
+        <v>7028490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1261,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124801857</v>
+        <v>124802067</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>74885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1281,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437882</v>
+        <v>437900</v>
       </c>
       <c r="R7" t="n">
-        <v>7028436</v>
+        <v>7028398</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802848</v>
+        <v>124801717</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,21 +1402,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1450,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437865</v>
+        <v>437880</v>
       </c>
       <c r="R8" t="n">
-        <v>7028297</v>
+        <v>7028440</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802943</v>
+        <v>124806329</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,43 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437861</v>
+        <v>437744</v>
       </c>
       <c r="R9" t="n">
-        <v>7028295</v>
+        <v>7028312</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1611,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1621,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124807432</v>
+        <v>124806603</v>
       </c>
       <c r="B10" t="n">
-        <v>78891</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,35 +1632,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>283</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1702,13 +1674,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437768</v>
+        <v>437790</v>
       </c>
       <c r="R10" t="n">
-        <v>7028490</v>
+        <v>7028422</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1747,12 +1719,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124801643</v>
+        <v>124801857</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,46 +1767,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437865</v>
+        <v>437882</v>
       </c>
       <c r="R11" t="n">
-        <v>7028458</v>
+        <v>7028436</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1863,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1836,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805246</v>
+        <v>124801891</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1921,34 +1884,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437817</v>
+        <v>437896</v>
       </c>
       <c r="R12" t="n">
-        <v>7028282</v>
+        <v>7028421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1980,7 +1957,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1990,12 +1967,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802466</v>
+        <v>124802608</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,25 +2011,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2062,13 +2039,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437886</v>
+        <v>437883</v>
       </c>
       <c r="R13" t="n">
-        <v>7028342</v>
+        <v>7028325</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2097,7 +2074,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,12 +2084,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2116,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124801717</v>
+        <v>124806928</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,25 +2128,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2179,10 +2156,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437880</v>
+        <v>437831</v>
       </c>
       <c r="R14" t="n">
-        <v>7028440</v>
+        <v>7028417</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2214,7 +2191,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2224,12 +2201,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802182</v>
+        <v>124806762</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2272,43 +2249,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437853</v>
+        <v>437830</v>
       </c>
       <c r="R15" t="n">
-        <v>7028377</v>
+        <v>7028451</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2340,7 +2308,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2350,12 +2318,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2382,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802067</v>
+        <v>124802342</v>
       </c>
       <c r="B16" t="n">
-        <v>74885</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,25 +2362,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2422,10 +2390,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437900</v>
+        <v>437861</v>
       </c>
       <c r="R16" t="n">
-        <v>7028398</v>
+        <v>7028347</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2425,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2435,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,10 +2467,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806762</v>
+        <v>124807390</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,21 +2483,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2539,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437830</v>
+        <v>437771</v>
       </c>
       <c r="R17" t="n">
-        <v>7028451</v>
+        <v>7028497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2574,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2584,12 +2552,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2616,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802608</v>
+        <v>124802211</v>
       </c>
       <c r="B18" t="n">
-        <v>79927</v>
+        <v>79919</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2600,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2624,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437883</v>
+        <v>437849</v>
       </c>
       <c r="R18" t="n">
-        <v>7028325</v>
+        <v>7028377</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,7 +2659,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2701,12 +2669,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804979</v>
+        <v>124802943</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2749,31 +2717,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2782,13 +2750,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437811</v>
+        <v>437861</v>
       </c>
       <c r="R19" t="n">
-        <v>7028294</v>
+        <v>7028295</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2817,7 +2785,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2827,12 +2795,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,10 +2827,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802211</v>
+        <v>124804979</v>
       </c>
       <c r="B20" t="n">
-        <v>79919</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2871,41 +2839,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437849</v>
+        <v>437811</v>
       </c>
       <c r="R20" t="n">
-        <v>7028377</v>
+        <v>7028294</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2934,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2944,12 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802526</v>
+        <v>124802330</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2992,43 +2969,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437884</v>
+        <v>437866</v>
       </c>
       <c r="R21" t="n">
-        <v>7028332</v>
+        <v>7028363</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -3060,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3070,12 +3038,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3102,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124807783</v>
+        <v>124804958</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3118,31 +3086,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3151,13 +3115,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437870</v>
+        <v>437804</v>
       </c>
       <c r="R22" t="n">
-        <v>7028581</v>
+        <v>7028292</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3186,7 +3150,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3196,12 +3160,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3228,10 +3192,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124807102</v>
+        <v>124802526</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3244,37 +3208,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437750</v>
+        <v>437884</v>
       </c>
       <c r="R23" t="n">
-        <v>7028464</v>
+        <v>7028332</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3303,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3313,12 +3286,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3345,7 +3318,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802401</v>
+        <v>124802848</v>
       </c>
       <c r="B24" t="n">
         <v>91012</v>
@@ -3385,13 +3358,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437856</v>
+        <v>437865</v>
       </c>
       <c r="R24" t="n">
-        <v>7028363</v>
+        <v>7028297</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3420,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3430,12 +3403,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3462,10 +3435,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124806928</v>
+        <v>124805246</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,25 +3447,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3502,10 +3475,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437831</v>
+        <v>437817</v>
       </c>
       <c r="R25" t="n">
-        <v>7028417</v>
+        <v>7028282</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3537,7 +3510,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3547,12 +3520,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,10 +3552,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802342</v>
+        <v>124805236</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3595,21 +3568,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3619,10 +3592,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437861</v>
+        <v>437817</v>
       </c>
       <c r="R26" t="n">
-        <v>7028347</v>
+        <v>7028282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3654,7 +3627,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3664,12 +3637,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3696,10 +3669,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802330</v>
+        <v>124807102</v>
       </c>
       <c r="B27" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3712,21 +3685,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3736,13 +3709,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437866</v>
+        <v>437750</v>
       </c>
       <c r="R27" t="n">
-        <v>7028363</v>
+        <v>7028464</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3771,7 +3744,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3781,12 +3754,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124806329</v>
+        <v>124801643</v>
       </c>
       <c r="B28" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3829,34 +3802,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437744</v>
+        <v>437865</v>
       </c>
       <c r="R28" t="n">
-        <v>7028312</v>
+        <v>7028458</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3888,7 +3870,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,12 +3880,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,10 +3912,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124801891</v>
+        <v>124807783</v>
       </c>
       <c r="B29" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3946,26 +3928,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3973,24 +3955,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437896</v>
+        <v>437870</v>
       </c>
       <c r="R29" t="n">
-        <v>7028421</v>
+        <v>7028581</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4019,7 +3996,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4029,12 +4006,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,10 +4038,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124807390</v>
+        <v>124806977</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>78891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4077,34 +4054,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437771</v>
+        <v>437826</v>
       </c>
       <c r="R30" t="n">
-        <v>7028497</v>
+        <v>7028421</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4136,7 +4127,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4137,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4169,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124807162</v>
+        <v>124802182</v>
       </c>
       <c r="B31" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4194,34 +4185,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437731</v>
+        <v>437853</v>
       </c>
       <c r="R31" t="n">
-        <v>7028449</v>
+        <v>7028377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802466</v>
+        <v>124802401</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437886</v>
+        <v>437856</v>
       </c>
       <c r="R3" t="n">
-        <v>7028342</v>
+        <v>7028363</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802401</v>
+        <v>124802466</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437856</v>
+        <v>437886</v>
       </c>
       <c r="R4" t="n">
-        <v>7028363</v>
+        <v>7028342</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802109</v>
+        <v>124802943</v>
       </c>
       <c r="B2" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437857</v>
+        <v>437861</v>
       </c>
       <c r="R2" t="n">
-        <v>7028393</v>
+        <v>7028295</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802401</v>
+        <v>124802342</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437856</v>
+        <v>437861</v>
       </c>
       <c r="R3" t="n">
-        <v>7028363</v>
+        <v>7028347</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802466</v>
+        <v>124805246</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437886</v>
+        <v>437817</v>
       </c>
       <c r="R4" t="n">
-        <v>7028342</v>
+        <v>7028282</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124807162</v>
+        <v>124802526</v>
       </c>
       <c r="B5" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,37 +1051,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437731</v>
+        <v>437884</v>
       </c>
       <c r="R5" t="n">
-        <v>7028449</v>
+        <v>7028332</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807432</v>
+        <v>124807102</v>
       </c>
       <c r="B6" t="n">
-        <v>78891</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,46 +1177,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437768</v>
+        <v>437750</v>
       </c>
       <c r="R6" t="n">
-        <v>7028490</v>
+        <v>7028464</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802067</v>
+        <v>124805236</v>
       </c>
       <c r="B7" t="n">
-        <v>74885</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,25 +1290,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437900</v>
+        <v>437817</v>
       </c>
       <c r="R7" t="n">
-        <v>7028398</v>
+        <v>7028282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124801717</v>
+        <v>124802211</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>79919</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,25 +1407,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437880</v>
+        <v>437849</v>
       </c>
       <c r="R8" t="n">
-        <v>7028440</v>
+        <v>7028377</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1480,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806329</v>
+        <v>124802608</v>
       </c>
       <c r="B9" t="n">
-        <v>78891</v>
+        <v>79927</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,25 +1524,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,13 +1552,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437744</v>
+        <v>437883</v>
       </c>
       <c r="R9" t="n">
-        <v>7028312</v>
+        <v>7028325</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1597,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1751,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124801857</v>
+        <v>124802848</v>
       </c>
       <c r="B11" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,21 +1776,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1791,13 +1800,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437882</v>
+        <v>437865</v>
       </c>
       <c r="R11" t="n">
-        <v>7028436</v>
+        <v>7028297</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1826,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,12 +1845,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124801891</v>
+        <v>124801643</v>
       </c>
       <c r="B12" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,26 +1893,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1911,24 +1920,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437896</v>
+        <v>437865</v>
       </c>
       <c r="R12" t="n">
-        <v>7028421</v>
+        <v>7028458</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1957,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1967,12 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802608</v>
+        <v>124801891</v>
       </c>
       <c r="B13" t="n">
-        <v>79927</v>
+        <v>78891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,38 +2015,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437883</v>
+        <v>437896</v>
       </c>
       <c r="R13" t="n">
-        <v>7028325</v>
+        <v>7028421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2084,12 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124806928</v>
+        <v>124802401</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,25 +2146,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2156,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437831</v>
+        <v>437856</v>
       </c>
       <c r="R14" t="n">
-        <v>7028417</v>
+        <v>7028363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2191,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2201,12 +2219,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,10 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806762</v>
+        <v>124807390</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2249,21 +2267,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2273,10 +2291,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437830</v>
+        <v>437771</v>
       </c>
       <c r="R15" t="n">
-        <v>7028451</v>
+        <v>7028497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2308,7 +2326,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2318,12 +2336,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802342</v>
+        <v>124802330</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,21 +2384,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2390,13 +2408,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437861</v>
+        <v>437866</v>
       </c>
       <c r="R16" t="n">
-        <v>7028347</v>
+        <v>7028363</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2425,7 +2443,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2435,12 +2453,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2467,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807390</v>
+        <v>124806762</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2483,21 +2501,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2507,10 +2525,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437771</v>
+        <v>437830</v>
       </c>
       <c r="R17" t="n">
-        <v>7028497</v>
+        <v>7028451</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2560,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,12 +2570,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2584,10 +2602,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802211</v>
+        <v>124806329</v>
       </c>
       <c r="B18" t="n">
-        <v>79919</v>
+        <v>78891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,25 +2614,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2624,13 +2642,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437849</v>
+        <v>437744</v>
       </c>
       <c r="R18" t="n">
-        <v>7028377</v>
+        <v>7028312</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,7 +2677,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,12 +2687,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,7 +2719,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124802943</v>
+        <v>124802466</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2734,26 +2752,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437861</v>
+        <v>437886</v>
       </c>
       <c r="R19" t="n">
-        <v>7028295</v>
+        <v>7028342</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2785,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2795,12 +2804,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2827,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804979</v>
+        <v>124801717</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>74901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2843,46 +2852,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437811</v>
+        <v>437880</v>
       </c>
       <c r="R20" t="n">
-        <v>7028294</v>
+        <v>7028440</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802330</v>
+        <v>124807783</v>
       </c>
       <c r="B21" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,34 +2969,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437866</v>
+        <v>437870</v>
       </c>
       <c r="R21" t="n">
-        <v>7028363</v>
+        <v>7028581</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -3028,7 +3037,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,12 +3047,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3079,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804958</v>
+        <v>124804979</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3086,16 +3095,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3103,10 +3112,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3115,13 +3128,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437804</v>
+        <v>437811</v>
       </c>
       <c r="R22" t="n">
-        <v>7028292</v>
+        <v>7028294</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3150,7 +3163,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3160,12 +3173,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3192,7 +3205,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802526</v>
+        <v>124802182</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3241,13 +3254,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437884</v>
+        <v>437853</v>
       </c>
       <c r="R23" t="n">
-        <v>7028332</v>
+        <v>7028377</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3276,7 +3289,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,12 +3299,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,10 +3331,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802848</v>
+        <v>124802067</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>74885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,25 +3343,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3358,13 +3371,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437865</v>
+        <v>437900</v>
       </c>
       <c r="R24" t="n">
-        <v>7028297</v>
+        <v>7028398</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3393,7 +3406,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,12 +3416,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3435,10 +3448,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124805246</v>
+        <v>124802109</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>96227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,25 +3460,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3475,10 +3488,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437817</v>
+        <v>437857</v>
       </c>
       <c r="R25" t="n">
-        <v>7028282</v>
+        <v>7028393</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,7 +3523,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3520,12 +3533,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3552,10 +3565,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124805236</v>
+        <v>124807162</v>
       </c>
       <c r="B26" t="n">
-        <v>77743</v>
+        <v>77753</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3568,21 +3581,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3592,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437817</v>
+        <v>437731</v>
       </c>
       <c r="R26" t="n">
-        <v>7028282</v>
+        <v>7028449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3627,7 +3640,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3637,12 +3650,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,10 +3682,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124807102</v>
+        <v>124801857</v>
       </c>
       <c r="B27" t="n">
-        <v>91008</v>
+        <v>77743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,21 +3698,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3709,13 +3722,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437750</v>
+        <v>437882</v>
       </c>
       <c r="R27" t="n">
-        <v>7028464</v>
+        <v>7028436</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3744,7 +3757,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3754,12 +3767,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3786,10 +3799,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124801643</v>
+        <v>124806977</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3802,26 +3815,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3829,19 +3842,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437865</v>
+        <v>437826</v>
       </c>
       <c r="R28" t="n">
-        <v>7028458</v>
+        <v>7028421</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3870,7 +3888,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3880,12 +3898,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3912,10 +3930,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124807783</v>
+        <v>124807432</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3928,26 +3946,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3961,13 +3979,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437870</v>
+        <v>437768</v>
       </c>
       <c r="R29" t="n">
-        <v>7028581</v>
+        <v>7028490</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3996,7 +4014,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4006,12 +4024,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4038,10 +4056,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124806977</v>
+        <v>124804958</v>
       </c>
       <c r="B30" t="n">
-        <v>78891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4054,36 +4072,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4092,13 +4101,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437826</v>
+        <v>437804</v>
       </c>
       <c r="R30" t="n">
-        <v>7028421</v>
+        <v>7028292</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4127,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4137,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4169,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124802182</v>
+        <v>124806928</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4181,47 +4190,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437853</v>
+        <v>437831</v>
       </c>
       <c r="R31" t="n">
-        <v>7028377</v>
+        <v>7028417</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802943</v>
+        <v>124802526</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437861</v>
+        <v>437884</v>
       </c>
       <c r="R2" t="n">
-        <v>7028295</v>
+        <v>7028332</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802342</v>
+        <v>124806329</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437861</v>
+        <v>437744</v>
       </c>
       <c r="R3" t="n">
-        <v>7028347</v>
+        <v>7028312</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124805246</v>
+        <v>124805236</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>77743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802526</v>
+        <v>124806928</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,50 +1047,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437884</v>
+        <v>437831</v>
       </c>
       <c r="R5" t="n">
-        <v>7028332</v>
+        <v>7028417</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807102</v>
+        <v>124807390</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,21 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,13 +1192,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437750</v>
+        <v>437771</v>
       </c>
       <c r="R6" t="n">
-        <v>7028464</v>
+        <v>7028497</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124805236</v>
+        <v>124805246</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,21 +1285,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1353,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1395,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802211</v>
+        <v>124806977</v>
       </c>
       <c r="B8" t="n">
-        <v>79919</v>
+        <v>78891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,38 +1398,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437849</v>
+        <v>437826</v>
       </c>
       <c r="R8" t="n">
-        <v>7028377</v>
+        <v>7028421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,12 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802608</v>
+        <v>124807162</v>
       </c>
       <c r="B9" t="n">
-        <v>79927</v>
+        <v>77753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,25 +1529,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437883</v>
+        <v>437731</v>
       </c>
       <c r="R9" t="n">
-        <v>7028325</v>
+        <v>7028449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,12 +1602,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124806603</v>
+        <v>124801891</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,40 +1646,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1683,13 +1688,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437790</v>
+        <v>437896</v>
       </c>
       <c r="R10" t="n">
-        <v>7028422</v>
+        <v>7028421</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,12 +1733,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802848</v>
+        <v>124807102</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,21 +1781,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437865</v>
+        <v>437750</v>
       </c>
       <c r="R11" t="n">
-        <v>7028297</v>
+        <v>7028464</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,12 +1850,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124801643</v>
+        <v>124804958</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,31 +1898,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1926,13 +1927,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437865</v>
+        <v>437804</v>
       </c>
       <c r="R12" t="n">
-        <v>7028458</v>
+        <v>7028292</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,7 +1962,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +1972,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,10 +2004,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124801891</v>
+        <v>124801717</v>
       </c>
       <c r="B13" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,48 +2020,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437896</v>
+        <v>437880</v>
       </c>
       <c r="R13" t="n">
-        <v>7028421</v>
+        <v>7028440</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2092,7 +2079,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2089,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802401</v>
+        <v>124802067</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>74885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,25 +2133,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +2161,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437856</v>
+        <v>437900</v>
       </c>
       <c r="R14" t="n">
-        <v>7028363</v>
+        <v>7028398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,7 +2196,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2219,12 +2206,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,10 +2238,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124807390</v>
+        <v>124802401</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,21 +2254,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2291,10 +2278,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437771</v>
+        <v>437856</v>
       </c>
       <c r="R15" t="n">
-        <v>7028497</v>
+        <v>7028363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,7 +2313,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2336,12 +2323,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,10 +2355,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802330</v>
+        <v>124802943</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2384,37 +2371,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437866</v>
+        <v>437861</v>
       </c>
       <c r="R16" t="n">
-        <v>7028363</v>
+        <v>7028295</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2443,7 +2439,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2453,12 +2449,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806762</v>
+        <v>124807432</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>78891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,34 +2497,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437830</v>
+        <v>437768</v>
       </c>
       <c r="R17" t="n">
-        <v>7028451</v>
+        <v>7028490</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2560,7 +2565,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2570,12 +2575,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,10 +2607,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124806329</v>
+        <v>124802848</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,21 +2623,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2642,10 +2647,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437744</v>
+        <v>437865</v>
       </c>
       <c r="R18" t="n">
-        <v>7028312</v>
+        <v>7028297</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2677,7 +2682,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2687,12 +2692,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2719,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124802466</v>
+        <v>124806762</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2735,21 +2740,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2759,13 +2764,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437886</v>
+        <v>437830</v>
       </c>
       <c r="R19" t="n">
-        <v>7028342</v>
+        <v>7028451</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2794,7 +2799,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,12 +2809,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124801717</v>
+        <v>124802182</v>
       </c>
       <c r="B20" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,34 +2857,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437880</v>
+        <v>437853</v>
       </c>
       <c r="R20" t="n">
-        <v>7028440</v>
+        <v>7028377</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2925,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2935,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2967,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124807783</v>
+        <v>124802608</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2965,50 +2979,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437870</v>
+        <v>437883</v>
       </c>
       <c r="R21" t="n">
-        <v>7028581</v>
+        <v>7028325</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3037,7 +3042,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3047,12 +3052,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3079,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804979</v>
+        <v>124802211</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>79919</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,50 +3096,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437811</v>
+        <v>437849</v>
       </c>
       <c r="R22" t="n">
-        <v>7028294</v>
+        <v>7028377</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3163,7 +3159,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3173,12 +3169,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3205,10 +3201,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802182</v>
+        <v>124802342</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,43 +3217,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437853</v>
+        <v>437861</v>
       </c>
       <c r="R23" t="n">
-        <v>7028377</v>
+        <v>7028347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3289,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3299,12 +3286,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3331,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802067</v>
+        <v>124807783</v>
       </c>
       <c r="B24" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3343,41 +3330,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437900</v>
+        <v>437870</v>
       </c>
       <c r="R24" t="n">
-        <v>7028398</v>
+        <v>7028581</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3406,7 +3402,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3416,12 +3412,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3448,10 +3444,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802109</v>
+        <v>124806603</v>
       </c>
       <c r="B25" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3460,41 +3456,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437857</v>
+        <v>437790</v>
       </c>
       <c r="R25" t="n">
-        <v>7028393</v>
+        <v>7028422</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3523,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3533,12 +3543,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,10 +3575,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124807162</v>
+        <v>124801643</v>
       </c>
       <c r="B26" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3581,37 +3591,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437731</v>
+        <v>437865</v>
       </c>
       <c r="R26" t="n">
-        <v>7028449</v>
+        <v>7028458</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3640,7 +3659,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3650,12 +3669,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3799,10 +3818,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124806977</v>
+        <v>124802466</v>
       </c>
       <c r="B28" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3815,51 +3834,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437826</v>
+        <v>437886</v>
       </c>
       <c r="R28" t="n">
-        <v>7028421</v>
+        <v>7028342</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3888,7 +3893,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,12 +3903,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,10 +3935,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124807432</v>
+        <v>124802330</v>
       </c>
       <c r="B29" t="n">
-        <v>78891</v>
+        <v>88359</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3946,46 +3951,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437768</v>
+        <v>437866</v>
       </c>
       <c r="R29" t="n">
-        <v>7028490</v>
+        <v>7028363</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4014,7 +4010,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4024,12 +4020,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4056,10 +4052,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124804958</v>
+        <v>124804979</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4072,16 +4068,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4089,10 +4085,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437804</v>
+        <v>437811</v>
       </c>
       <c r="R30" t="n">
-        <v>7028292</v>
+        <v>7028294</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124806928</v>
+        <v>124802109</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>96227</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4194,21 +4194,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437831</v>
+        <v>437857</v>
       </c>
       <c r="R31" t="n">
-        <v>7028417</v>
+        <v>7028393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802526</v>
+        <v>124802330</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437884</v>
+        <v>437866</v>
       </c>
       <c r="R2" t="n">
-        <v>7028332</v>
+        <v>7028363</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124806329</v>
+        <v>124802943</v>
       </c>
       <c r="B3" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +808,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437744</v>
+        <v>437861</v>
       </c>
       <c r="R3" t="n">
-        <v>7028312</v>
+        <v>7028295</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124805236</v>
+        <v>124801857</v>
       </c>
       <c r="B4" t="n">
         <v>77743</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437817</v>
+        <v>437882</v>
       </c>
       <c r="R4" t="n">
-        <v>7028282</v>
+        <v>7028436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124806928</v>
+        <v>124801643</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,41 +1047,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437831</v>
+        <v>437865</v>
       </c>
       <c r="R5" t="n">
-        <v>7028417</v>
+        <v>7028458</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807390</v>
+        <v>124802067</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1173,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437771</v>
+        <v>437900</v>
       </c>
       <c r="R6" t="n">
-        <v>7028497</v>
+        <v>7028398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124805246</v>
+        <v>124807102</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,21 +1294,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,13 +1318,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437817</v>
+        <v>437750</v>
       </c>
       <c r="R7" t="n">
-        <v>7028282</v>
+        <v>7028464</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124806977</v>
+        <v>124804958</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,36 +1411,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437826</v>
+        <v>437804</v>
       </c>
       <c r="R8" t="n">
-        <v>7028421</v>
+        <v>7028292</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124807162</v>
+        <v>124806603</v>
       </c>
       <c r="B9" t="n">
-        <v>77753</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,41 +1529,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>314</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437731</v>
+        <v>437790</v>
       </c>
       <c r="R9" t="n">
-        <v>7028449</v>
+        <v>7028422</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1606,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,12 +1616,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124801891</v>
+        <v>124807783</v>
       </c>
       <c r="B10" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,26 +1664,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1677,24 +1691,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437896</v>
+        <v>437870</v>
       </c>
       <c r="R10" t="n">
-        <v>7028421</v>
+        <v>7028581</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,12 +1742,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124807102</v>
+        <v>124801891</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>78891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,37 +1790,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437750</v>
+        <v>437896</v>
       </c>
       <c r="R11" t="n">
-        <v>7028464</v>
+        <v>7028421</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1840,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804958</v>
+        <v>124807432</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1898,27 +1921,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1927,13 +1954,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437804</v>
+        <v>437768</v>
       </c>
       <c r="R12" t="n">
-        <v>7028292</v>
+        <v>7028490</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1962,7 +1989,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1972,12 +1999,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,10 +2031,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124801717</v>
+        <v>124802526</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2020,37 +2047,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437880</v>
+        <v>437884</v>
       </c>
       <c r="R13" t="n">
-        <v>7028440</v>
+        <v>7028332</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2079,7 +2115,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2089,12 +2125,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802067</v>
+        <v>124804979</v>
       </c>
       <c r="B14" t="n">
-        <v>74885</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2133,41 +2169,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437900</v>
+        <v>437811</v>
       </c>
       <c r="R14" t="n">
-        <v>7028398</v>
+        <v>7028294</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2196,7 +2241,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2206,12 +2251,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,10 +2283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802401</v>
+        <v>124802608</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79927</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2250,25 +2295,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2278,10 +2323,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437856</v>
+        <v>437883</v>
       </c>
       <c r="R15" t="n">
-        <v>7028363</v>
+        <v>7028325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,7 +2358,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2323,12 +2368,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,10 +2400,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802943</v>
+        <v>124802211</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2367,50 +2412,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437861</v>
+        <v>437849</v>
       </c>
       <c r="R16" t="n">
-        <v>7028295</v>
+        <v>7028377</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2439,7 +2475,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2449,12 +2485,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,10 +2517,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807432</v>
+        <v>124802182</v>
       </c>
       <c r="B17" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2497,26 +2533,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2530,10 +2566,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437768</v>
+        <v>437853</v>
       </c>
       <c r="R17" t="n">
-        <v>7028490</v>
+        <v>7028377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2565,7 +2601,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2575,12 +2611,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2607,10 +2643,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802848</v>
+        <v>124802342</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2623,21 +2659,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2647,13 +2683,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437865</v>
+        <v>437861</v>
       </c>
       <c r="R18" t="n">
-        <v>7028297</v>
+        <v>7028347</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2682,7 +2718,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2692,12 +2728,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2724,10 +2760,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806762</v>
+        <v>124801717</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2740,21 +2776,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2764,10 +2800,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437830</v>
+        <v>437880</v>
       </c>
       <c r="R19" t="n">
-        <v>7028451</v>
+        <v>7028440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,7 +2835,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2809,12 +2845,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2841,10 +2877,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802182</v>
+        <v>124806762</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2857,43 +2893,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437853</v>
+        <v>437830</v>
       </c>
       <c r="R20" t="n">
-        <v>7028377</v>
+        <v>7028451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2925,7 +2952,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2935,12 +2962,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2967,10 +2994,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802608</v>
+        <v>124805236</v>
       </c>
       <c r="B21" t="n">
-        <v>79927</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2979,25 +3006,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3007,10 +3034,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437883</v>
+        <v>437817</v>
       </c>
       <c r="R21" t="n">
-        <v>7028325</v>
+        <v>7028282</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3042,7 +3069,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3052,12 +3079,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,10 +3111,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802211</v>
+        <v>124802401</v>
       </c>
       <c r="B22" t="n">
-        <v>79919</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3123,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3124,10 +3151,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437849</v>
+        <v>437856</v>
       </c>
       <c r="R22" t="n">
-        <v>7028377</v>
+        <v>7028363</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3186,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3169,12 +3196,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802342</v>
+        <v>124807390</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3217,21 +3244,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3241,10 +3268,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437861</v>
+        <v>437771</v>
       </c>
       <c r="R23" t="n">
-        <v>7028347</v>
+        <v>7028497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3303,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,12 +3313,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,10 +3345,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124807783</v>
+        <v>124806928</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,50 +3357,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437870</v>
+        <v>437831</v>
       </c>
       <c r="R24" t="n">
-        <v>7028581</v>
+        <v>7028417</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3402,7 +3420,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3412,12 +3430,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3444,10 +3462,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124806603</v>
+        <v>124802109</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3456,55 +3474,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437790</v>
+        <v>437857</v>
       </c>
       <c r="R25" t="n">
-        <v>7028422</v>
+        <v>7028393</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,12 +3547,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3575,7 +3579,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124801643</v>
+        <v>124802466</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3608,26 +3612,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437865</v>
+        <v>437886</v>
       </c>
       <c r="R26" t="n">
-        <v>7028458</v>
+        <v>7028342</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3659,7 +3654,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3669,12 +3664,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3701,10 +3696,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124801857</v>
+        <v>124806977</v>
       </c>
       <c r="B27" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3717,34 +3712,48 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437882</v>
+        <v>437826</v>
       </c>
       <c r="R27" t="n">
-        <v>7028436</v>
+        <v>7028421</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3776,7 +3785,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3786,12 +3795,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3818,10 +3827,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802466</v>
+        <v>124806329</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3834,21 +3843,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3858,10 +3867,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437886</v>
+        <v>437744</v>
       </c>
       <c r="R28" t="n">
-        <v>7028342</v>
+        <v>7028312</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3893,7 +3902,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3903,12 +3912,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3935,10 +3944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124802330</v>
+        <v>124802848</v>
       </c>
       <c r="B29" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3951,21 +3960,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3975,13 +3984,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437866</v>
+        <v>437865</v>
       </c>
       <c r="R29" t="n">
-        <v>7028363</v>
+        <v>7028297</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4010,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4020,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4052,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124804979</v>
+        <v>124805246</v>
       </c>
       <c r="B30" t="n">
-        <v>56714</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4068,46 +4077,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437811</v>
+        <v>437817</v>
       </c>
       <c r="R30" t="n">
-        <v>7028294</v>
+        <v>7028282</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124802109</v>
+        <v>124807162</v>
       </c>
       <c r="B31" t="n">
-        <v>96227</v>
+        <v>77753</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4190,25 +4190,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437857</v>
+        <v>437731</v>
       </c>
       <c r="R31" t="n">
-        <v>7028393</v>
+        <v>7028449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124807102</v>
+        <v>124804958</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,37 +1294,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437750</v>
+        <v>437804</v>
       </c>
       <c r="R7" t="n">
-        <v>7028464</v>
+        <v>7028292</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804958</v>
+        <v>124807102</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,42 +1416,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437804</v>
+        <v>437750</v>
       </c>
       <c r="R8" t="n">
-        <v>7028292</v>
+        <v>7028464</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1774,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124801891</v>
+        <v>124802526</v>
       </c>
       <c r="B11" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,26 +1790,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1817,24 +1817,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437896</v>
+        <v>437884</v>
       </c>
       <c r="R11" t="n">
-        <v>7028421</v>
+        <v>7028332</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124807432</v>
+        <v>124801891</v>
       </c>
       <c r="B12" t="n">
         <v>78891</v>
@@ -1948,16 +1943,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437768</v>
+        <v>437896</v>
       </c>
       <c r="R12" t="n">
-        <v>7028490</v>
+        <v>7028421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802526</v>
+        <v>124807432</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,26 +2047,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2080,13 +2080,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437884</v>
+        <v>437768</v>
       </c>
       <c r="R13" t="n">
-        <v>7028332</v>
+        <v>7028490</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802330</v>
+        <v>124805246</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437866</v>
+        <v>437817</v>
       </c>
       <c r="R2" t="n">
-        <v>7028363</v>
+        <v>7028282</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802943</v>
+        <v>124802608</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,50 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437861</v>
+        <v>437883</v>
       </c>
       <c r="R3" t="n">
-        <v>7028295</v>
+        <v>7028325</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124801857</v>
+        <v>124802848</v>
       </c>
       <c r="B4" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437882</v>
+        <v>437865</v>
       </c>
       <c r="R4" t="n">
-        <v>7028436</v>
+        <v>7028297</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124801643</v>
+        <v>124801891</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,26 +1042,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,19 +1069,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437865</v>
+        <v>437896</v>
       </c>
       <c r="R5" t="n">
-        <v>7028458</v>
+        <v>7028421</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802067</v>
+        <v>124807390</v>
       </c>
       <c r="B6" t="n">
-        <v>74885</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,25 +1169,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437900</v>
+        <v>437771</v>
       </c>
       <c r="R6" t="n">
-        <v>7028398</v>
+        <v>7028497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804958</v>
+        <v>124801857</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,42 +1290,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437804</v>
+        <v>437882</v>
       </c>
       <c r="R7" t="n">
-        <v>7028292</v>
+        <v>7028436</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,12 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124807102</v>
+        <v>124806603</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,41 +1403,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437750</v>
+        <v>437790</v>
       </c>
       <c r="R8" t="n">
-        <v>7028464</v>
+        <v>7028422</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,12 +1490,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1522,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806603</v>
+        <v>124806329</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,55 +1534,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437790</v>
+        <v>437744</v>
       </c>
       <c r="R9" t="n">
-        <v>7028422</v>
+        <v>7028312</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,12 +1607,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1639,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124807783</v>
+        <v>124802526</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1683,7 +1674,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1697,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437870</v>
+        <v>437884</v>
       </c>
       <c r="R10" t="n">
-        <v>7028581</v>
+        <v>7028332</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1732,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,12 +1733,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802526</v>
+        <v>124804979</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,31 +1781,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1823,13 +1814,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437884</v>
+        <v>437811</v>
       </c>
       <c r="R11" t="n">
-        <v>7028332</v>
+        <v>7028294</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1859,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124801891</v>
+        <v>124806928</v>
       </c>
       <c r="B12" t="n">
-        <v>78891</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,52 +1903,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437896</v>
+        <v>437831</v>
       </c>
       <c r="R12" t="n">
-        <v>7028421</v>
+        <v>7028417</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,12 +1976,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2031,10 +2008,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124807432</v>
+        <v>124807783</v>
       </c>
       <c r="B13" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,26 +2024,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2080,13 +2057,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437768</v>
+        <v>437870</v>
       </c>
       <c r="R13" t="n">
-        <v>7028490</v>
+        <v>7028581</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2115,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2125,12 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804979</v>
+        <v>124804958</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,16 +2150,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2190,14 +2167,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2206,13 +2179,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437811</v>
+        <v>437804</v>
       </c>
       <c r="R14" t="n">
-        <v>7028294</v>
+        <v>7028292</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2214,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2251,12 +2224,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802608</v>
+        <v>124805236</v>
       </c>
       <c r="B15" t="n">
-        <v>79927</v>
+        <v>77743</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,25 +2268,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2323,10 +2296,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437883</v>
+        <v>437817</v>
       </c>
       <c r="R15" t="n">
-        <v>7028325</v>
+        <v>7028282</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2358,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2368,12 +2341,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2400,10 +2373,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802211</v>
+        <v>124807162</v>
       </c>
       <c r="B16" t="n">
-        <v>79919</v>
+        <v>77753</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2412,25 +2385,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2440,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437849</v>
+        <v>437731</v>
       </c>
       <c r="R16" t="n">
-        <v>7028377</v>
+        <v>7028449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2475,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2485,12 +2458,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2517,10 +2490,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802182</v>
+        <v>124806977</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2533,26 +2506,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2560,16 +2533,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437853</v>
+        <v>437826</v>
       </c>
       <c r="R17" t="n">
-        <v>7028377</v>
+        <v>7028421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2601,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2611,12 +2589,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2643,10 +2621,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802342</v>
+        <v>124802401</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2659,21 +2637,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2683,10 +2661,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437861</v>
+        <v>437856</v>
       </c>
       <c r="R18" t="n">
-        <v>7028347</v>
+        <v>7028363</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,7 +2696,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2728,12 +2706,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2760,10 +2738,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124801717</v>
+        <v>124801643</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2776,37 +2754,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437880</v>
+        <v>437865</v>
       </c>
       <c r="R19" t="n">
-        <v>7028440</v>
+        <v>7028458</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2835,7 +2822,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2845,12 +2832,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2994,10 +2981,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805236</v>
+        <v>124807432</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3010,34 +2997,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437817</v>
+        <v>437768</v>
       </c>
       <c r="R21" t="n">
-        <v>7028282</v>
+        <v>7028490</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3069,7 +3065,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3079,12 +3075,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3111,10 +3107,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802401</v>
+        <v>124802330</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,21 +3123,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3151,13 +3147,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437856</v>
+        <v>437866</v>
       </c>
       <c r="R22" t="n">
         <v>7028363</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3186,7 +3182,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3196,12 +3192,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3228,10 +3224,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124807390</v>
+        <v>124802943</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3244,37 +3240,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437771</v>
+        <v>437861</v>
       </c>
       <c r="R23" t="n">
-        <v>7028497</v>
+        <v>7028295</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3303,7 +3308,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3313,12 +3318,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3345,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806928</v>
+        <v>124802182</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3357,38 +3362,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437831</v>
+        <v>437853</v>
       </c>
       <c r="R24" t="n">
-        <v>7028417</v>
+        <v>7028377</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3420,7 +3434,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3430,12 +3444,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3462,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802109</v>
+        <v>124802211</v>
       </c>
       <c r="B25" t="n">
-        <v>96227</v>
+        <v>79919</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3478,21 +3492,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3502,10 +3516,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437857</v>
+        <v>437849</v>
       </c>
       <c r="R25" t="n">
-        <v>7028393</v>
+        <v>7028377</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3537,7 +3551,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3547,12 +3561,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,10 +3593,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802466</v>
+        <v>124802067</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>74885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3591,25 +3605,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3619,13 +3633,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437886</v>
+        <v>437900</v>
       </c>
       <c r="R26" t="n">
-        <v>7028342</v>
+        <v>7028398</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3654,7 +3668,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3664,12 +3678,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3696,10 +3710,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124806977</v>
+        <v>124801717</v>
       </c>
       <c r="B27" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3712,48 +3726,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437826</v>
+        <v>437880</v>
       </c>
       <c r="R27" t="n">
-        <v>7028421</v>
+        <v>7028440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124806329</v>
+        <v>124807102</v>
       </c>
       <c r="B28" t="n">
-        <v>78891</v>
+        <v>91008</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437744</v>
+        <v>437750</v>
       </c>
       <c r="R28" t="n">
-        <v>7028312</v>
+        <v>7028464</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,10 +3944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124802848</v>
+        <v>124802342</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3984,13 +3984,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437865</v>
+        <v>437861</v>
       </c>
       <c r="R29" t="n">
-        <v>7028297</v>
+        <v>7028347</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124805246</v>
+        <v>124802466</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4077,21 +4077,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437817</v>
+        <v>437886</v>
       </c>
       <c r="R30" t="n">
-        <v>7028282</v>
+        <v>7028342</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124807162</v>
+        <v>124802109</v>
       </c>
       <c r="B31" t="n">
-        <v>77753</v>
+        <v>96227</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4190,25 +4190,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437731</v>
+        <v>437857</v>
       </c>
       <c r="R31" t="n">
-        <v>7028449</v>
+        <v>7028393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124805246</v>
+        <v>124802211</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>79919</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437817</v>
+        <v>437849</v>
       </c>
       <c r="R2" t="n">
-        <v>7028282</v>
+        <v>7028377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802848</v>
+        <v>124807102</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437865</v>
+        <v>437750</v>
       </c>
       <c r="R4" t="n">
-        <v>7028297</v>
+        <v>7028464</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124801891</v>
+        <v>124804979</v>
       </c>
       <c r="B5" t="n">
-        <v>78891</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,14 +1064,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437896</v>
+        <v>437811</v>
       </c>
       <c r="R5" t="n">
-        <v>7028421</v>
+        <v>7028294</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807390</v>
+        <v>124802182</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,34 +1168,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437771</v>
+        <v>437853</v>
       </c>
       <c r="R6" t="n">
-        <v>7028497</v>
+        <v>7028377</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124801857</v>
+        <v>124802109</v>
       </c>
       <c r="B7" t="n">
-        <v>77743</v>
+        <v>96227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,25 +1290,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1314,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437882</v>
+        <v>437857</v>
       </c>
       <c r="R7" t="n">
-        <v>7028436</v>
+        <v>7028393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124806603</v>
+        <v>124805246</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,55 +1407,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437790</v>
+        <v>437817</v>
       </c>
       <c r="R8" t="n">
-        <v>7028422</v>
+        <v>7028282</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,12 +1480,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806329</v>
+        <v>124806603</v>
       </c>
       <c r="B9" t="n">
-        <v>78891</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,41 +1524,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437744</v>
+        <v>437790</v>
       </c>
       <c r="R9" t="n">
-        <v>7028312</v>
+        <v>7028422</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,12 +1611,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,7 +1643,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802526</v>
+        <v>124802943</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1674,7 +1678,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1688,13 +1692,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437884</v>
+        <v>437861</v>
       </c>
       <c r="R10" t="n">
-        <v>7028332</v>
+        <v>7028295</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1727,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,12 +1737,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804979</v>
+        <v>124807783</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,31 +1785,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1814,13 +1818,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437811</v>
+        <v>437870</v>
       </c>
       <c r="R11" t="n">
-        <v>7028294</v>
+        <v>7028581</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,12 +1863,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124806928</v>
+        <v>124801643</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1903,41 +1907,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437831</v>
+        <v>437865</v>
       </c>
       <c r="R12" t="n">
-        <v>7028417</v>
+        <v>7028458</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1979,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,12 +1989,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2008,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124807783</v>
+        <v>124802848</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,46 +2037,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437870</v>
+        <v>437865</v>
       </c>
       <c r="R13" t="n">
-        <v>7028581</v>
+        <v>7028297</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2096,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2106,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804958</v>
+        <v>124806928</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,46 +2150,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437804</v>
+        <v>437831</v>
       </c>
       <c r="R14" t="n">
-        <v>7028292</v>
+        <v>7028417</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2214,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2224,12 +2223,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805236</v>
+        <v>124807390</v>
       </c>
       <c r="B15" t="n">
-        <v>77743</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2272,21 +2271,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2296,10 +2295,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437817</v>
+        <v>437771</v>
       </c>
       <c r="R15" t="n">
-        <v>7028282</v>
+        <v>7028497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,12 +2340,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124807162</v>
+        <v>124801891</v>
       </c>
       <c r="B16" t="n">
-        <v>77753</v>
+        <v>78891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2389,34 +2388,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437731</v>
+        <v>437896</v>
       </c>
       <c r="R16" t="n">
-        <v>7028449</v>
+        <v>7028421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2461,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2458,12 +2471,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806977</v>
+        <v>124802067</v>
       </c>
       <c r="B17" t="n">
-        <v>78891</v>
+        <v>74885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2502,52 +2515,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>283</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437826</v>
+        <v>437900</v>
       </c>
       <c r="R17" t="n">
-        <v>7028421</v>
+        <v>7028398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2579,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,12 +2588,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2621,10 +2620,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802401</v>
+        <v>124801857</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,21 +2636,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437856</v>
+        <v>437882</v>
       </c>
       <c r="R18" t="n">
-        <v>7028363</v>
+        <v>7028436</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2696,7 +2695,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2706,12 +2705,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2738,10 +2737,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124801643</v>
+        <v>124807162</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,46 +2753,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437865</v>
+        <v>437731</v>
       </c>
       <c r="R19" t="n">
-        <v>7028458</v>
+        <v>7028449</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2822,7 +2812,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2832,12 +2822,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2864,10 +2854,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124806762</v>
+        <v>124802330</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>88359</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,21 +2870,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2904,13 +2894,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437830</v>
+        <v>437866</v>
       </c>
       <c r="R20" t="n">
-        <v>7028451</v>
+        <v>7028363</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2939,7 +2929,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2949,12 +2939,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,7 +2971,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124807432</v>
+        <v>124806329</v>
       </c>
       <c r="B21" t="n">
         <v>78891</v>
@@ -3014,29 +3004,20 @@
           <t>(Degel.) Krog</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437768</v>
+        <v>437744</v>
       </c>
       <c r="R21" t="n">
-        <v>7028490</v>
+        <v>7028312</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3065,7 +3046,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3075,12 +3056,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,10 +3088,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802330</v>
+        <v>124807432</v>
       </c>
       <c r="B22" t="n">
-        <v>88359</v>
+        <v>78891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3123,37 +3104,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437866</v>
+        <v>437768</v>
       </c>
       <c r="R22" t="n">
-        <v>7028363</v>
+        <v>7028490</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3182,7 +3172,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3192,12 +3182,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3224,10 +3214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802943</v>
+        <v>124801717</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3240,46 +3230,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437861</v>
+        <v>437880</v>
       </c>
       <c r="R23" t="n">
-        <v>7028295</v>
+        <v>7028440</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3308,7 +3289,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3318,12 +3299,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,10 +3331,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802182</v>
+        <v>124805236</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3366,43 +3347,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437853</v>
+        <v>437817</v>
       </c>
       <c r="R24" t="n">
-        <v>7028377</v>
+        <v>7028282</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3434,7 +3406,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3444,12 +3416,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3476,10 +3448,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802211</v>
+        <v>124802401</v>
       </c>
       <c r="B25" t="n">
-        <v>79919</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3488,25 +3460,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3516,10 +3488,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437849</v>
+        <v>437856</v>
       </c>
       <c r="R25" t="n">
-        <v>7028377</v>
+        <v>7028363</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3551,7 +3523,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3561,12 +3533,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3593,10 +3565,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802067</v>
+        <v>124802342</v>
       </c>
       <c r="B26" t="n">
-        <v>74885</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3605,25 +3577,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3633,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437900</v>
+        <v>437861</v>
       </c>
       <c r="R26" t="n">
-        <v>7028398</v>
+        <v>7028347</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3668,7 +3640,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3678,12 +3650,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,10 +3682,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124801717</v>
+        <v>124802526</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,37 +3698,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437880</v>
+        <v>437884</v>
       </c>
       <c r="R27" t="n">
-        <v>7028440</v>
+        <v>7028332</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3785,7 +3766,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3795,12 +3776,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,10 +3808,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124807102</v>
+        <v>124802466</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3843,21 +3824,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3867,10 +3848,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437750</v>
+        <v>437886</v>
       </c>
       <c r="R28" t="n">
-        <v>7028464</v>
+        <v>7028342</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
@@ -3902,7 +3883,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3912,12 +3893,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,10 +3925,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124802342</v>
+        <v>124806977</v>
       </c>
       <c r="B29" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3960,34 +3941,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437861</v>
+        <v>437826</v>
       </c>
       <c r="R29" t="n">
-        <v>7028347</v>
+        <v>7028421</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4029,12 +4024,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,10 +4056,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124802466</v>
+        <v>124806762</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4077,21 +4072,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4101,13 +4096,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437886</v>
+        <v>437830</v>
       </c>
       <c r="R30" t="n">
-        <v>7028342</v>
+        <v>7028451</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4131,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4141,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4173,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124802109</v>
+        <v>124804958</v>
       </c>
       <c r="B31" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4190,41 +4185,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437857</v>
+        <v>437804</v>
       </c>
       <c r="R31" t="n">
-        <v>7028393</v>
+        <v>7028292</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802211</v>
+        <v>124801643</v>
       </c>
       <c r="B2" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437849</v>
+        <v>437865</v>
       </c>
       <c r="R2" t="n">
-        <v>7028377</v>
+        <v>7028458</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802608</v>
+        <v>124807432</v>
       </c>
       <c r="B3" t="n">
-        <v>79927</v>
+        <v>78891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437883</v>
+        <v>437768</v>
       </c>
       <c r="R3" t="n">
-        <v>7028325</v>
+        <v>7028490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124807102</v>
+        <v>124802211</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>79919</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437750</v>
+        <v>437849</v>
       </c>
       <c r="R4" t="n">
-        <v>7028464</v>
+        <v>7028377</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804979</v>
+        <v>124801857</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>77743</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,46 +1060,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437811</v>
+        <v>437882</v>
       </c>
       <c r="R5" t="n">
-        <v>7028294</v>
+        <v>7028436</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802182</v>
+        <v>124804958</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,31 +1177,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437853</v>
+        <v>437804</v>
       </c>
       <c r="R6" t="n">
-        <v>7028377</v>
+        <v>7028292</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802109</v>
+        <v>124806977</v>
       </c>
       <c r="B7" t="n">
-        <v>96227</v>
+        <v>78891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,38 +1295,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437857</v>
+        <v>437826</v>
       </c>
       <c r="R7" t="n">
-        <v>7028393</v>
+        <v>7028421</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124805246</v>
+        <v>124802848</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1430,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,13 +1454,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437817</v>
+        <v>437865</v>
       </c>
       <c r="R8" t="n">
-        <v>7028282</v>
+        <v>7028297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806603</v>
+        <v>124802401</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,55 +1543,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437790</v>
+        <v>437856</v>
       </c>
       <c r="R9" t="n">
-        <v>7028422</v>
+        <v>7028363</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,12 +1616,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802943</v>
+        <v>124802109</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,50 +1660,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437861</v>
+        <v>437857</v>
       </c>
       <c r="R10" t="n">
-        <v>7028295</v>
+        <v>7028393</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1737,12 +1733,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124807783</v>
+        <v>124806928</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,50 +1777,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437870</v>
+        <v>437831</v>
       </c>
       <c r="R11" t="n">
-        <v>7028581</v>
+        <v>7028417</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,12 +1850,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124801643</v>
+        <v>124804979</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,31 +1898,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1944,13 +1931,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437865</v>
+        <v>437811</v>
       </c>
       <c r="R12" t="n">
-        <v>7028458</v>
+        <v>7028294</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1979,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,12 +1976,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,10 +2008,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802848</v>
+        <v>124802526</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,37 +2024,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437865</v>
+        <v>437884</v>
       </c>
       <c r="R13" t="n">
-        <v>7028297</v>
+        <v>7028332</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2106,12 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2138,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124806928</v>
+        <v>124802067</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>74885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2154,21 +2150,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437831</v>
+        <v>437900</v>
       </c>
       <c r="R14" t="n">
-        <v>7028417</v>
+        <v>7028398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,12 +2219,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2255,10 +2251,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124807390</v>
+        <v>124802182</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,34 +2267,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437771</v>
+        <v>437853</v>
       </c>
       <c r="R15" t="n">
-        <v>7028497</v>
+        <v>7028377</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2340,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2503,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802067</v>
+        <v>124802466</v>
       </c>
       <c r="B17" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,25 +2520,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,13 +2548,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437900</v>
+        <v>437886</v>
       </c>
       <c r="R17" t="n">
-        <v>7028398</v>
+        <v>7028342</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,12 +2593,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,7 +2625,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124801857</v>
+        <v>124805236</v>
       </c>
       <c r="B18" t="n">
         <v>77743</v>
@@ -2660,10 +2665,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437882</v>
+        <v>437817</v>
       </c>
       <c r="R18" t="n">
-        <v>7028436</v>
+        <v>7028282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2695,7 +2700,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2705,12 +2710,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2737,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124807162</v>
+        <v>124807102</v>
       </c>
       <c r="B19" t="n">
-        <v>77753</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2753,21 +2758,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2777,13 +2782,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437731</v>
+        <v>437750</v>
       </c>
       <c r="R19" t="n">
-        <v>7028449</v>
+        <v>7028464</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2812,7 +2817,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2822,12 +2827,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802330</v>
+        <v>124805246</v>
       </c>
       <c r="B20" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2870,21 +2875,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2894,13 +2899,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437866</v>
+        <v>437817</v>
       </c>
       <c r="R20" t="n">
-        <v>7028363</v>
+        <v>7028282</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2929,7 +2934,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2939,12 +2944,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124806329</v>
+        <v>124801717</v>
       </c>
       <c r="B21" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2987,21 +2992,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3011,13 +3016,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437744</v>
+        <v>437880</v>
       </c>
       <c r="R21" t="n">
-        <v>7028312</v>
+        <v>7028440</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3056,12 +3061,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3088,10 +3093,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124807432</v>
+        <v>124802943</v>
       </c>
       <c r="B22" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3104,26 +3109,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3137,13 +3142,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437768</v>
+        <v>437861</v>
       </c>
       <c r="R22" t="n">
-        <v>7028490</v>
+        <v>7028295</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3172,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3182,12 +3187,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3214,10 +3219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124801717</v>
+        <v>124806603</v>
       </c>
       <c r="B23" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3226,41 +3231,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437880</v>
+        <v>437790</v>
       </c>
       <c r="R23" t="n">
-        <v>7028440</v>
+        <v>7028422</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3289,7 +3308,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3299,12 +3318,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3331,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124805236</v>
+        <v>124806762</v>
       </c>
       <c r="B24" t="n">
-        <v>77743</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3347,21 +3366,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3371,10 +3390,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437817</v>
+        <v>437830</v>
       </c>
       <c r="R24" t="n">
-        <v>7028282</v>
+        <v>7028451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3406,7 +3425,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3416,12 +3435,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3448,10 +3467,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802401</v>
+        <v>124802330</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3464,21 +3483,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3488,13 +3507,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437856</v>
+        <v>437866</v>
       </c>
       <c r="R25" t="n">
         <v>7028363</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3523,7 +3542,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3533,12 +3552,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3682,10 +3701,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802526</v>
+        <v>124802608</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3694,50 +3713,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437884</v>
+        <v>437883</v>
       </c>
       <c r="R27" t="n">
-        <v>7028332</v>
+        <v>7028325</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3766,7 +3776,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3776,12 +3786,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3808,7 +3818,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802466</v>
+        <v>124807783</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3841,20 +3851,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437886</v>
+        <v>437870</v>
       </c>
       <c r="R28" t="n">
-        <v>7028342</v>
+        <v>7028581</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3883,7 +3902,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3893,7 +3912,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3925,10 +3944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124806977</v>
+        <v>124807162</v>
       </c>
       <c r="B29" t="n">
-        <v>78891</v>
+        <v>77753</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3941,48 +3960,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437826</v>
+        <v>437731</v>
       </c>
       <c r="R29" t="n">
-        <v>7028421</v>
+        <v>7028449</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4014,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4024,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4056,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124806762</v>
+        <v>124806329</v>
       </c>
       <c r="B30" t="n">
-        <v>91008</v>
+        <v>78891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4072,21 +4077,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4096,13 +4101,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437830</v>
+        <v>437744</v>
       </c>
       <c r="R30" t="n">
-        <v>7028451</v>
+        <v>7028312</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4131,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4141,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4173,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124804958</v>
+        <v>124807390</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4189,42 +4194,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437804</v>
+        <v>437771</v>
       </c>
       <c r="R31" t="n">
-        <v>7028292</v>
+        <v>7028497</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124807432</v>
+        <v>124802211</v>
       </c>
       <c r="B3" t="n">
-        <v>78891</v>
+        <v>79919</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +813,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>283</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437768</v>
+        <v>437849</v>
       </c>
       <c r="R3" t="n">
-        <v>7028490</v>
+        <v>7028377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802211</v>
+        <v>124807432</v>
       </c>
       <c r="B4" t="n">
-        <v>79919</v>
+        <v>78891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,38 +930,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437849</v>
+        <v>437768</v>
       </c>
       <c r="R4" t="n">
-        <v>7028377</v>
+        <v>7028490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802401</v>
+        <v>124802109</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,25 +1543,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437856</v>
+        <v>437857</v>
       </c>
       <c r="R9" t="n">
-        <v>7028363</v>
+        <v>7028393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802109</v>
+        <v>124802401</v>
       </c>
       <c r="B10" t="n">
-        <v>96227</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,25 +1660,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437857</v>
+        <v>437856</v>
       </c>
       <c r="R10" t="n">
-        <v>7028393</v>
+        <v>7028363</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2134,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802067</v>
+        <v>124801891</v>
       </c>
       <c r="B14" t="n">
-        <v>74885</v>
+        <v>78891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,38 +2146,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437900</v>
+        <v>437896</v>
       </c>
       <c r="R14" t="n">
-        <v>7028398</v>
+        <v>7028421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2219,12 +2233,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,10 +2265,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802182</v>
+        <v>124802067</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>74885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,47 +2277,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437853</v>
+        <v>437900</v>
       </c>
       <c r="R15" t="n">
-        <v>7028377</v>
+        <v>7028398</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,12 +2350,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,10 +2382,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124801891</v>
+        <v>124802182</v>
       </c>
       <c r="B16" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2393,26 +2398,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2420,21 +2425,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437896</v>
+        <v>437853</v>
       </c>
       <c r="R16" t="n">
-        <v>7028421</v>
+        <v>7028377</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3093,10 +3093,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802943</v>
+        <v>124806762</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3109,46 +3109,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437861</v>
+        <v>437830</v>
       </c>
       <c r="R22" t="n">
-        <v>7028295</v>
+        <v>7028451</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3177,7 +3168,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,12 +3178,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3219,10 +3210,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124806603</v>
+        <v>124802943</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3231,40 +3222,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3273,13 +3259,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437790</v>
+        <v>437861</v>
       </c>
       <c r="R23" t="n">
-        <v>7028422</v>
+        <v>7028295</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3308,7 +3294,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3318,12 +3304,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,10 +3336,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806762</v>
+        <v>124806603</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3362,41 +3348,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437830</v>
+        <v>437790</v>
       </c>
       <c r="R24" t="n">
-        <v>7028451</v>
+        <v>7028422</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3467,10 +3467,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802330</v>
+        <v>124802342</v>
       </c>
       <c r="B25" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3483,21 +3483,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437866</v>
+        <v>437861</v>
       </c>
       <c r="R25" t="n">
-        <v>7028363</v>
+        <v>7028347</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3584,10 +3584,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802342</v>
+        <v>124802330</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>88359</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437861</v>
+        <v>437866</v>
       </c>
       <c r="R26" t="n">
-        <v>7028347</v>
+        <v>7028363</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124801643</v>
+        <v>124807390</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437865</v>
+        <v>437771</v>
       </c>
       <c r="R2" t="n">
-        <v>7028458</v>
+        <v>7028497</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802211</v>
+        <v>124805236</v>
       </c>
       <c r="B3" t="n">
-        <v>79919</v>
+        <v>77743</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437849</v>
+        <v>437817</v>
       </c>
       <c r="R3" t="n">
-        <v>7028377</v>
+        <v>7028282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124807432</v>
+        <v>124802067</v>
       </c>
       <c r="B4" t="n">
-        <v>78891</v>
+        <v>74885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,47 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>283</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437768</v>
+        <v>437900</v>
       </c>
       <c r="R4" t="n">
-        <v>7028490</v>
+        <v>7028398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124801857</v>
+        <v>124801891</v>
       </c>
       <c r="B5" t="n">
-        <v>77743</v>
+        <v>78891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,34 +1042,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437882</v>
+        <v>437896</v>
       </c>
       <c r="R5" t="n">
-        <v>7028436</v>
+        <v>7028421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804958</v>
+        <v>124807102</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,42 +1173,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437804</v>
+        <v>437750</v>
       </c>
       <c r="R6" t="n">
-        <v>7028292</v>
+        <v>7028464</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124806977</v>
+        <v>124802211</v>
       </c>
       <c r="B7" t="n">
-        <v>78891</v>
+        <v>79919</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,52 +1286,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>283</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437826</v>
+        <v>437849</v>
       </c>
       <c r="R7" t="n">
-        <v>7028421</v>
+        <v>7028377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,12 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802848</v>
+        <v>124802466</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1454,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437865</v>
+        <v>437886</v>
       </c>
       <c r="R8" t="n">
-        <v>7028297</v>
+        <v>7028342</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1489,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,12 +1476,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802109</v>
+        <v>124806762</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437857</v>
+        <v>437830</v>
       </c>
       <c r="R9" t="n">
-        <v>7028393</v>
+        <v>7028451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,12 +1593,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802401</v>
+        <v>124802182</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,34 +1641,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437856</v>
+        <v>437853</v>
       </c>
       <c r="R10" t="n">
-        <v>7028363</v>
+        <v>7028377</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,12 +1719,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124806928</v>
+        <v>124807783</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1777,41 +1763,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437831</v>
+        <v>437870</v>
       </c>
       <c r="R11" t="n">
-        <v>7028417</v>
+        <v>7028581</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,12 +1845,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804979</v>
+        <v>124802401</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1898,46 +1893,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437811</v>
+        <v>437856</v>
       </c>
       <c r="R12" t="n">
-        <v>7028294</v>
+        <v>7028363</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1952,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,12 +1962,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2008,10 +1994,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802526</v>
+        <v>124802342</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,46 +2010,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437884</v>
+        <v>437861</v>
       </c>
       <c r="R13" t="n">
-        <v>7028332</v>
+        <v>7028347</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2069,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2079,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2111,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124801891</v>
+        <v>124802330</v>
       </c>
       <c r="B14" t="n">
-        <v>78891</v>
+        <v>88359</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2150,51 +2127,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437896</v>
+        <v>437866</v>
       </c>
       <c r="R14" t="n">
-        <v>7028421</v>
+        <v>7028363</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2223,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,12 +2196,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,10 +2228,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802067</v>
+        <v>124801643</v>
       </c>
       <c r="B15" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,41 +2240,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437900</v>
+        <v>437865</v>
       </c>
       <c r="R15" t="n">
-        <v>7028398</v>
+        <v>7028458</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,7 +2312,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2350,12 +2322,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2382,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802182</v>
+        <v>124804958</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2398,31 +2370,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2431,13 +2399,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437853</v>
+        <v>437804</v>
       </c>
       <c r="R16" t="n">
-        <v>7028377</v>
+        <v>7028292</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2466,7 +2434,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2476,12 +2444,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802466</v>
+        <v>124801717</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2524,21 +2492,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2548,13 +2516,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437886</v>
+        <v>437880</v>
       </c>
       <c r="R17" t="n">
-        <v>7028342</v>
+        <v>7028440</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2583,7 +2551,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2593,12 +2561,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2625,10 +2593,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805236</v>
+        <v>124802109</v>
       </c>
       <c r="B18" t="n">
-        <v>77743</v>
+        <v>96227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,25 +2605,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2665,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437817</v>
+        <v>437857</v>
       </c>
       <c r="R18" t="n">
-        <v>7028282</v>
+        <v>7028393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2700,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2710,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2742,10 +2710,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124807102</v>
+        <v>124807432</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>78891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2758,37 +2726,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437750</v>
+        <v>437768</v>
       </c>
       <c r="R19" t="n">
-        <v>7028464</v>
+        <v>7028490</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2817,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2827,12 +2804,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,10 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124805246</v>
+        <v>124807162</v>
       </c>
       <c r="B20" t="n">
-        <v>74901</v>
+        <v>77753</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2875,21 +2852,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2899,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437817</v>
+        <v>437731</v>
       </c>
       <c r="R20" t="n">
-        <v>7028282</v>
+        <v>7028449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2934,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2944,12 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124801717</v>
+        <v>124802848</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2992,21 +2969,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3016,13 +2993,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437880</v>
+        <v>437865</v>
       </c>
       <c r="R21" t="n">
-        <v>7028440</v>
+        <v>7028297</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3051,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3061,12 +3038,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806762</v>
+        <v>124801857</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>77743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3109,21 +3086,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3133,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437830</v>
+        <v>437882</v>
       </c>
       <c r="R22" t="n">
-        <v>7028451</v>
+        <v>7028436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3168,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3178,12 +3155,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802943</v>
+        <v>124802608</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3222,50 +3199,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437861</v>
+        <v>437883</v>
       </c>
       <c r="R23" t="n">
-        <v>7028295</v>
+        <v>7028325</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3294,7 +3262,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3304,12 +3272,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3336,10 +3304,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806603</v>
+        <v>124806977</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3348,40 +3316,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3390,13 +3358,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437790</v>
+        <v>437826</v>
       </c>
       <c r="R24" t="n">
-        <v>7028422</v>
+        <v>7028421</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3425,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3435,12 +3403,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3467,10 +3435,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802342</v>
+        <v>124806329</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>78891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3483,21 +3451,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3507,13 +3475,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437861</v>
+        <v>437744</v>
       </c>
       <c r="R25" t="n">
-        <v>7028347</v>
+        <v>7028312</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3542,7 +3510,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3552,12 +3520,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3584,10 +3552,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802330</v>
+        <v>124805246</v>
       </c>
       <c r="B26" t="n">
-        <v>88359</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,21 +3568,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3624,13 +3592,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437866</v>
+        <v>437817</v>
       </c>
       <c r="R26" t="n">
-        <v>7028363</v>
+        <v>7028282</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3659,7 +3627,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3669,12 +3637,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3701,10 +3669,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802608</v>
+        <v>124806928</v>
       </c>
       <c r="B27" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3717,21 +3685,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3741,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437883</v>
+        <v>437831</v>
       </c>
       <c r="R27" t="n">
-        <v>7028325</v>
+        <v>7028417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3776,7 +3744,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3786,12 +3754,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3818,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124807783</v>
+        <v>124804979</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3834,31 +3802,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3867,13 +3835,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437870</v>
+        <v>437811</v>
       </c>
       <c r="R28" t="n">
-        <v>7028581</v>
+        <v>7028294</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3902,7 +3870,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3912,12 +3880,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,10 +3912,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124807162</v>
+        <v>124802943</v>
       </c>
       <c r="B29" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3960,37 +3928,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437731</v>
+        <v>437861</v>
       </c>
       <c r="R29" t="n">
-        <v>7028449</v>
+        <v>7028295</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4019,7 +3996,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4029,12 +4006,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,10 +4038,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124806329</v>
+        <v>124802526</v>
       </c>
       <c r="B30" t="n">
-        <v>78891</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4077,37 +4054,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437744</v>
+        <v>437884</v>
       </c>
       <c r="R30" t="n">
-        <v>7028312</v>
+        <v>7028332</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4136,7 +4122,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4132,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124807390</v>
+        <v>124806603</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4190,41 +4176,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437771</v>
+        <v>437790</v>
       </c>
       <c r="R31" t="n">
-        <v>7028497</v>
+        <v>7028422</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -2953,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802848</v>
+        <v>124801857</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,21 +2969,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437865</v>
+        <v>437882</v>
       </c>
       <c r="R21" t="n">
-        <v>7028297</v>
+        <v>7028436</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124801857</v>
+        <v>124802848</v>
       </c>
       <c r="B22" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437882</v>
+        <v>437865</v>
       </c>
       <c r="R22" t="n">
-        <v>7028436</v>
+        <v>7028297</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3912,10 +3912,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124802943</v>
+        <v>124806603</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3924,35 +3924,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3961,13 +3966,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437861</v>
+        <v>437790</v>
       </c>
       <c r="R29" t="n">
-        <v>7028295</v>
+        <v>7028422</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3996,7 +4001,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4006,12 +4011,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4164,10 +4169,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124806603</v>
+        <v>124802943</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4176,40 +4181,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437790</v>
+        <v>437861</v>
       </c>
       <c r="R31" t="n">
-        <v>7028422</v>
+        <v>7028295</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124807390</v>
+        <v>124802526</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437771</v>
+        <v>437884</v>
       </c>
       <c r="R2" t="n">
-        <v>7028497</v>
+        <v>7028332</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124805236</v>
+        <v>124802109</v>
       </c>
       <c r="B3" t="n">
-        <v>77743</v>
+        <v>96227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437817</v>
+        <v>437857</v>
       </c>
       <c r="R3" t="n">
-        <v>7028282</v>
+        <v>7028393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802067</v>
+        <v>124806329</v>
       </c>
       <c r="B4" t="n">
-        <v>74885</v>
+        <v>78891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437900</v>
+        <v>437744</v>
       </c>
       <c r="R4" t="n">
-        <v>7028398</v>
+        <v>7028312</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124801891</v>
+        <v>124806603</v>
       </c>
       <c r="B5" t="n">
-        <v>78891</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,40 +1047,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437896</v>
+        <v>437790</v>
       </c>
       <c r="R5" t="n">
-        <v>7028421</v>
+        <v>7028422</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1134,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807102</v>
+        <v>124805246</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,21 +1182,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,13 +1206,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437750</v>
+        <v>437817</v>
       </c>
       <c r="R6" t="n">
-        <v>7028464</v>
+        <v>7028282</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802211</v>
+        <v>124807390</v>
       </c>
       <c r="B7" t="n">
-        <v>79919</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1314,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437849</v>
+        <v>437771</v>
       </c>
       <c r="R7" t="n">
-        <v>7028377</v>
+        <v>7028497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,7 +1400,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802466</v>
+        <v>124801643</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1424,17 +1433,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437886</v>
+        <v>437865</v>
       </c>
       <c r="R8" t="n">
-        <v>7028342</v>
+        <v>7028458</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1466,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,12 +1494,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806762</v>
+        <v>124802342</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1542,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437830</v>
+        <v>437861</v>
       </c>
       <c r="R9" t="n">
-        <v>7028451</v>
+        <v>7028347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,12 +1611,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802182</v>
+        <v>124801891</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,26 +1659,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1668,16 +1686,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437853</v>
+        <v>437896</v>
       </c>
       <c r="R10" t="n">
-        <v>7028377</v>
+        <v>7028421</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,12 +1742,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124807783</v>
+        <v>124802330</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,43 +1790,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437870</v>
+        <v>437866</v>
       </c>
       <c r="R11" t="n">
-        <v>7028581</v>
+        <v>7028363</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -1835,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,12 +1859,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,10 +1891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802401</v>
+        <v>124807432</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,34 +1907,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437856</v>
+        <v>437768</v>
       </c>
       <c r="R12" t="n">
-        <v>7028363</v>
+        <v>7028490</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1962,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802342</v>
+        <v>124802182</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,34 +2033,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437861</v>
+        <v>437853</v>
       </c>
       <c r="R13" t="n">
-        <v>7028347</v>
+        <v>7028377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,7 +2101,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2079,12 +2111,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,10 +2143,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802330</v>
+        <v>124806762</v>
       </c>
       <c r="B14" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2127,21 +2159,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2151,13 +2183,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437866</v>
+        <v>437830</v>
       </c>
       <c r="R14" t="n">
-        <v>7028363</v>
+        <v>7028451</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2186,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,12 +2228,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124801643</v>
+        <v>124804958</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2244,31 +2276,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2277,13 +2305,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437865</v>
+        <v>437804</v>
       </c>
       <c r="R15" t="n">
-        <v>7028458</v>
+        <v>7028292</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2312,7 +2340,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2322,12 +2350,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,10 +2382,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804958</v>
+        <v>124802067</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>74885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,46 +2394,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437804</v>
+        <v>437900</v>
       </c>
       <c r="R16" t="n">
-        <v>7028292</v>
+        <v>7028398</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2434,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2444,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2476,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124801717</v>
+        <v>124807783</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,37 +2515,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437880</v>
+        <v>437870</v>
       </c>
       <c r="R17" t="n">
-        <v>7028440</v>
+        <v>7028581</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2551,7 +2583,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2561,12 +2593,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802109</v>
+        <v>124806977</v>
       </c>
       <c r="B18" t="n">
-        <v>96227</v>
+        <v>78891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2605,38 +2637,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437857</v>
+        <v>437826</v>
       </c>
       <c r="R18" t="n">
-        <v>7028393</v>
+        <v>7028421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,7 +2714,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2724,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,10 +2756,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124807432</v>
+        <v>124805236</v>
       </c>
       <c r="B19" t="n">
-        <v>78891</v>
+        <v>77743</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2726,43 +2772,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437768</v>
+        <v>437817</v>
       </c>
       <c r="R19" t="n">
-        <v>7028490</v>
+        <v>7028282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,7 +2831,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,12 +2841,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,10 +2873,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124807162</v>
+        <v>124802466</v>
       </c>
       <c r="B20" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2852,21 +2889,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,13 +2913,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437731</v>
+        <v>437886</v>
       </c>
       <c r="R20" t="n">
-        <v>7028449</v>
+        <v>7028342</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2911,7 +2948,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2958,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2990,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124801857</v>
+        <v>124802401</v>
       </c>
       <c r="B21" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,21 +3006,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2993,10 +3030,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437882</v>
+        <v>437856</v>
       </c>
       <c r="R21" t="n">
-        <v>7028436</v>
+        <v>7028363</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,7 +3065,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,12 +3075,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3107,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802848</v>
+        <v>124802608</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>79927</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3082,25 +3119,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,13 +3147,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437865</v>
+        <v>437883</v>
       </c>
       <c r="R22" t="n">
-        <v>7028297</v>
+        <v>7028325</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3145,7 +3182,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,12 +3192,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3224,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802608</v>
+        <v>124802211</v>
       </c>
       <c r="B23" t="n">
-        <v>79927</v>
+        <v>79919</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,21 +3240,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3227,10 +3264,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437883</v>
+        <v>437849</v>
       </c>
       <c r="R23" t="n">
-        <v>7028325</v>
+        <v>7028377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3262,7 +3299,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3272,12 +3309,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3304,10 +3341,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806977</v>
+        <v>124801717</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>74901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3320,48 +3357,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437826</v>
+        <v>437880</v>
       </c>
       <c r="R24" t="n">
-        <v>7028421</v>
+        <v>7028440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,7 +3416,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,12 +3426,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3435,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124806329</v>
+        <v>124807102</v>
       </c>
       <c r="B25" t="n">
-        <v>78891</v>
+        <v>91008</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3451,21 +3474,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3475,10 +3498,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437744</v>
+        <v>437750</v>
       </c>
       <c r="R25" t="n">
-        <v>7028312</v>
+        <v>7028464</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
@@ -3510,7 +3533,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3520,12 +3543,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3552,10 +3575,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124805246</v>
+        <v>124806928</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3564,25 +3587,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3592,10 +3615,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437817</v>
+        <v>437831</v>
       </c>
       <c r="R26" t="n">
-        <v>7028282</v>
+        <v>7028417</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3627,7 +3650,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3637,12 +3660,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,10 +3692,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124806928</v>
+        <v>124802943</v>
       </c>
       <c r="B27" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3681,41 +3704,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437831</v>
+        <v>437861</v>
       </c>
       <c r="R27" t="n">
-        <v>7028417</v>
+        <v>7028295</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3744,7 +3776,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3754,12 +3786,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3912,10 +3944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124806603</v>
+        <v>124801857</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3924,55 +3956,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437790</v>
+        <v>437882</v>
       </c>
       <c r="R29" t="n">
-        <v>7028422</v>
+        <v>7028436</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4001,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4011,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4043,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124802526</v>
+        <v>124807162</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4059,46 +4077,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437884</v>
+        <v>437731</v>
       </c>
       <c r="R30" t="n">
-        <v>7028332</v>
+        <v>7028449</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4127,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4137,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4169,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124802943</v>
+        <v>124802848</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4185,43 +4194,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437861</v>
+        <v>437865</v>
       </c>
       <c r="R31" t="n">
-        <v>7028295</v>
+        <v>7028297</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802526</v>
+        <v>124804958</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437884</v>
+        <v>437804</v>
       </c>
       <c r="R2" t="n">
-        <v>7028332</v>
+        <v>7028292</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802109</v>
+        <v>124807102</v>
       </c>
       <c r="B3" t="n">
-        <v>96227</v>
+        <v>91162</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437857</v>
+        <v>437750</v>
       </c>
       <c r="R3" t="n">
-        <v>7028393</v>
+        <v>7028464</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124806329</v>
+        <v>124807162</v>
       </c>
       <c r="B4" t="n">
-        <v>78891</v>
+        <v>77889</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437744</v>
+        <v>437731</v>
       </c>
       <c r="R4" t="n">
-        <v>7028312</v>
+        <v>7028449</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124806603</v>
+        <v>124802943</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,40 +1043,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437790</v>
+        <v>437861</v>
       </c>
       <c r="R5" t="n">
-        <v>7028422</v>
+        <v>7028295</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805246</v>
+        <v>124804979</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>56828</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,37 +1173,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437817</v>
+        <v>437811</v>
       </c>
       <c r="R6" t="n">
-        <v>7028282</v>
+        <v>7028294</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124807390</v>
+        <v>124805236</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>77879</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,21 +1299,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437771</v>
+        <v>437817</v>
       </c>
       <c r="R7" t="n">
-        <v>7028497</v>
+        <v>7028282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124801643</v>
+        <v>124806329</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,43 +1416,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437865</v>
+        <v>437744</v>
       </c>
       <c r="R8" t="n">
-        <v>7028458</v>
+        <v>7028312</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1484,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,12 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802342</v>
+        <v>124807783</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,37 +1533,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437861</v>
+        <v>437870</v>
       </c>
       <c r="R9" t="n">
-        <v>7028347</v>
+        <v>7028581</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124801891</v>
+        <v>124802109</v>
       </c>
       <c r="B10" t="n">
-        <v>78891</v>
+        <v>96395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,52 +1655,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>283</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437896</v>
+        <v>437857</v>
       </c>
       <c r="R10" t="n">
-        <v>7028421</v>
+        <v>7028393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1732,7 +1718,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,12 +1728,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802330</v>
+        <v>124802608</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>80064</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1786,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1814,13 +1800,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437866</v>
+        <v>437883</v>
       </c>
       <c r="R11" t="n">
-        <v>7028363</v>
+        <v>7028325</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,12 +1845,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,10 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124807432</v>
+        <v>124802401</v>
       </c>
       <c r="B12" t="n">
-        <v>78891</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,43 +1893,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437768</v>
+        <v>437856</v>
       </c>
       <c r="R12" t="n">
-        <v>7028490</v>
+        <v>7028363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1952,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +1962,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,10 +1994,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802182</v>
+        <v>124801891</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,26 +2010,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2060,16 +2037,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437853</v>
+        <v>437896</v>
       </c>
       <c r="R13" t="n">
-        <v>7028377</v>
+        <v>7028421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2101,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2111,12 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2143,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124806762</v>
+        <v>124802330</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>88512</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2159,21 +2141,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2183,13 +2165,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437830</v>
+        <v>437866</v>
       </c>
       <c r="R14" t="n">
-        <v>7028451</v>
+        <v>7028363</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2218,7 +2200,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,12 +2210,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,10 +2242,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804958</v>
+        <v>124807390</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,42 +2258,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437804</v>
+        <v>437771</v>
       </c>
       <c r="R15" t="n">
-        <v>7028292</v>
+        <v>7028497</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,7 +2317,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2350,12 +2327,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2382,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802067</v>
+        <v>124805246</v>
       </c>
       <c r="B16" t="n">
-        <v>74885</v>
+        <v>75025</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,25 +2371,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2422,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437900</v>
+        <v>437817</v>
       </c>
       <c r="R16" t="n">
-        <v>7028398</v>
+        <v>7028282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2434,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2444,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807783</v>
+        <v>124806928</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,50 +2488,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437870</v>
+        <v>437831</v>
       </c>
       <c r="R17" t="n">
-        <v>7028581</v>
+        <v>7028417</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2583,7 +2551,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2593,12 +2561,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2625,10 +2593,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124806977</v>
+        <v>124806762</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>91162</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2641,48 +2609,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437826</v>
+        <v>437830</v>
       </c>
       <c r="R18" t="n">
-        <v>7028421</v>
+        <v>7028451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2714,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2724,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2756,10 +2710,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805236</v>
+        <v>124802211</v>
       </c>
       <c r="B19" t="n">
-        <v>77743</v>
+        <v>80056</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2768,25 +2722,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2796,10 +2750,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437817</v>
+        <v>437849</v>
       </c>
       <c r="R19" t="n">
-        <v>7028282</v>
+        <v>7028377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2831,7 +2785,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2841,12 +2795,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2873,10 +2827,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802466</v>
+        <v>124807432</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2889,37 +2843,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437886</v>
+        <v>437768</v>
       </c>
       <c r="R20" t="n">
-        <v>7028342</v>
+        <v>7028490</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2948,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2958,12 +2921,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2990,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802401</v>
+        <v>124801857</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>77879</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3006,21 +2969,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3030,10 +2993,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437856</v>
+        <v>437882</v>
       </c>
       <c r="R21" t="n">
-        <v>7028363</v>
+        <v>7028436</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3065,7 +3028,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3075,12 +3038,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802608</v>
+        <v>124802067</v>
       </c>
       <c r="B22" t="n">
-        <v>79927</v>
+        <v>75009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3123,21 +3086,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3147,10 +3110,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437883</v>
+        <v>437900</v>
       </c>
       <c r="R22" t="n">
-        <v>7028325</v>
+        <v>7028398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3182,7 +3145,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3192,12 +3155,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3224,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802211</v>
+        <v>124806977</v>
       </c>
       <c r="B23" t="n">
-        <v>79919</v>
+        <v>79028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3236,38 +3199,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437849</v>
+        <v>437826</v>
       </c>
       <c r="R23" t="n">
-        <v>7028377</v>
+        <v>7028421</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3299,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3309,12 +3286,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124801717</v>
+        <v>124802466</v>
       </c>
       <c r="B24" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3357,21 +3334,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3381,13 +3358,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437880</v>
+        <v>437886</v>
       </c>
       <c r="R24" t="n">
-        <v>7028440</v>
+        <v>7028342</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3416,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3426,12 +3403,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3458,10 +3435,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124807102</v>
+        <v>124806603</v>
       </c>
       <c r="B25" t="n">
-        <v>91008</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3470,41 +3447,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437750</v>
+        <v>437790</v>
       </c>
       <c r="R25" t="n">
-        <v>7028464</v>
+        <v>7028422</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3533,7 +3524,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3543,12 +3534,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3575,10 +3566,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124806928</v>
+        <v>124802526</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3587,41 +3578,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437831</v>
+        <v>437884</v>
       </c>
       <c r="R26" t="n">
-        <v>7028417</v>
+        <v>7028332</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,10 +3692,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802943</v>
+        <v>124801643</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437861</v>
+        <v>437865</v>
       </c>
       <c r="R27" t="n">
-        <v>7028295</v>
+        <v>7028458</v>
       </c>
       <c r="S27" t="n">
         <v>8</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3818,10 +3818,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124804979</v>
+        <v>124802342</v>
       </c>
       <c r="B28" t="n">
-        <v>56714</v>
+        <v>75025</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3834,46 +3834,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437811</v>
+        <v>437861</v>
       </c>
       <c r="R28" t="n">
-        <v>7028294</v>
+        <v>7028347</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3902,7 +3893,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3912,12 +3903,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,10 +3935,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124801857</v>
+        <v>124801717</v>
       </c>
       <c r="B29" t="n">
-        <v>77743</v>
+        <v>75025</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3960,21 +3951,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3984,10 +3975,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437882</v>
+        <v>437880</v>
       </c>
       <c r="R29" t="n">
-        <v>7028436</v>
+        <v>7028440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4034,7 +4025,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4061,10 +4052,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124807162</v>
+        <v>124802182</v>
       </c>
       <c r="B30" t="n">
-        <v>77753</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4077,34 +4068,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437731</v>
+        <v>437853</v>
       </c>
       <c r="R30" t="n">
-        <v>7028449</v>
+        <v>7028377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4181,7 +4181,7 @@
         <v>124802848</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124804958</v>
+        <v>124806329</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>79028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437804</v>
+        <v>437744</v>
       </c>
       <c r="R2" t="n">
-        <v>7028292</v>
+        <v>7028312</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124807102</v>
+        <v>124806762</v>
       </c>
       <c r="B3" t="n">
         <v>91162</v>
@@ -837,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437750</v>
+        <v>437830</v>
       </c>
       <c r="R3" t="n">
-        <v>7028464</v>
+        <v>7028451</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grov död gran i gammal fuktig granskog</t>
+          <t>På gammal naturlig granstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124807162</v>
+        <v>124802466</v>
       </c>
       <c r="B4" t="n">
-        <v>77889</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437731</v>
+        <v>437886</v>
       </c>
       <c r="R4" t="n">
-        <v>7028449</v>
+        <v>7028342</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802943</v>
+        <v>124806603</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,35 +1038,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437861</v>
+        <v>437790</v>
       </c>
       <c r="R5" t="n">
-        <v>7028295</v>
+        <v>7028422</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804979</v>
+        <v>124801891</v>
       </c>
       <c r="B6" t="n">
-        <v>56828</v>
+        <v>79028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,21 +1173,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1195,9 +1195,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1206,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437811</v>
+        <v>437896</v>
       </c>
       <c r="R6" t="n">
-        <v>7028294</v>
+        <v>7028421</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1256,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I gammal gransumpskog</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124805236</v>
+        <v>124801643</v>
       </c>
       <c r="B7" t="n">
-        <v>77879</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,37 +1304,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437817</v>
+        <v>437865</v>
       </c>
       <c r="R7" t="n">
-        <v>7028282</v>
+        <v>7028458</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,12 +1382,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124806329</v>
+        <v>124806928</v>
       </c>
       <c r="B8" t="n">
-        <v>79028</v>
+        <v>80057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1426,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,13 +1454,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437744</v>
+        <v>437831</v>
       </c>
       <c r="R8" t="n">
-        <v>7028312</v>
+        <v>7028417</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal sumpgranskog</t>
+          <t>På klen björklåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124807783</v>
+        <v>124804979</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>56828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,31 +1547,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1566,13 +1580,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437870</v>
+        <v>437811</v>
       </c>
       <c r="R9" t="n">
-        <v>7028581</v>
+        <v>7028294</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,12 +1625,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>I gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802109</v>
+        <v>124801857</v>
       </c>
       <c r="B10" t="n">
-        <v>96395</v>
+        <v>77879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,25 +1669,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437857</v>
+        <v>437882</v>
       </c>
       <c r="R10" t="n">
-        <v>7028393</v>
+        <v>7028436</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,12 +1742,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802608</v>
+        <v>124805236</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
+        <v>77879</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,25 +1786,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1800,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437883</v>
+        <v>437817</v>
       </c>
       <c r="R11" t="n">
-        <v>7028325</v>
+        <v>7028282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,12 +1859,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På klen gammal rönn i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,10 +1891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802401</v>
+        <v>124802067</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>75009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,25 +1903,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1917,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437856</v>
+        <v>437900</v>
       </c>
       <c r="R12" t="n">
-        <v>7028363</v>
+        <v>7028398</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1962,12 +1976,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,10 +2008,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124801891</v>
+        <v>124802848</v>
       </c>
       <c r="B13" t="n">
-        <v>79028</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,51 +2024,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437896</v>
+        <v>437865</v>
       </c>
       <c r="R13" t="n">
-        <v>7028421</v>
+        <v>7028297</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802330</v>
+        <v>124806977</v>
       </c>
       <c r="B14" t="n">
-        <v>88512</v>
+        <v>79028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,37 +2141,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437866</v>
+        <v>437826</v>
       </c>
       <c r="R14" t="n">
-        <v>7028363</v>
+        <v>7028421</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2200,7 +2214,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2210,12 +2224,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124807390</v>
+        <v>124802342</v>
       </c>
       <c r="B15" t="n">
-        <v>91184</v>
+        <v>75025</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2258,21 +2272,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2282,10 +2296,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437771</v>
+        <v>437861</v>
       </c>
       <c r="R15" t="n">
-        <v>7028497</v>
+        <v>7028347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2327,12 +2341,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På bark på stam av död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2476,10 +2490,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806928</v>
+        <v>124802943</v>
       </c>
       <c r="B17" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2488,41 +2502,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437831</v>
+        <v>437861</v>
       </c>
       <c r="R17" t="n">
-        <v>7028417</v>
+        <v>7028295</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2551,7 +2574,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2561,12 +2584,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På klen björklåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog, friskfuktig mark med vitmossa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124806762</v>
+        <v>124802211</v>
       </c>
       <c r="B18" t="n">
-        <v>91162</v>
+        <v>80056</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2605,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437830</v>
+        <v>437849</v>
       </c>
       <c r="R18" t="n">
-        <v>7028451</v>
+        <v>7028377</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,7 +2691,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2701,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal naturlig granstubbe i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,10 +2733,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124802211</v>
+        <v>124807783</v>
       </c>
       <c r="B19" t="n">
-        <v>80056</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2722,41 +2745,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437849</v>
+        <v>437870</v>
       </c>
       <c r="R19" t="n">
-        <v>7028377</v>
+        <v>7028581</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2785,7 +2817,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2795,12 +2827,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog i nordsluttning</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2827,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124807432</v>
+        <v>124801717</v>
       </c>
       <c r="B20" t="n">
-        <v>79028</v>
+        <v>75025</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2843,43 +2875,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437768</v>
+        <v>437880</v>
       </c>
       <c r="R20" t="n">
-        <v>7028490</v>
+        <v>7028440</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2911,7 +2934,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,12 +2944,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124801857</v>
+        <v>124807432</v>
       </c>
       <c r="B21" t="n">
-        <v>77879</v>
+        <v>79028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,34 +2992,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437882</v>
+        <v>437768</v>
       </c>
       <c r="R21" t="n">
-        <v>7028436</v>
+        <v>7028490</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3028,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3038,12 +3070,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På tunna kvistar på gammal senvuxen levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3070,10 +3102,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802067</v>
+        <v>124802608</v>
       </c>
       <c r="B22" t="n">
-        <v>75009</v>
+        <v>80064</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3086,21 +3118,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3110,10 +3142,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437900</v>
+        <v>437883</v>
       </c>
       <c r="R22" t="n">
-        <v>7028398</v>
+        <v>7028325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3155,12 +3187,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>På klen gammal rönn i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124806977</v>
+        <v>124802182</v>
       </c>
       <c r="B23" t="n">
-        <v>79028</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,26 +3235,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3230,21 +3262,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437826</v>
+        <v>437853</v>
       </c>
       <c r="R23" t="n">
-        <v>7028421</v>
+        <v>7028377</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3303,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,12 +3313,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På tunn död gren på gammal senvuxen gran i gammal fuktig granskog</t>
+          <t>På gammal gran i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,10 +3345,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802466</v>
+        <v>124804958</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3334,37 +3361,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437886</v>
+        <v>437804</v>
       </c>
       <c r="R24" t="n">
-        <v>7028342</v>
+        <v>7028292</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3393,7 +3425,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,12 +3435,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt med gamla men även årsfärska ringhack från 0,5 till 6 meter upp i ca 150-årig gran i gransumpskog. Rikligt med döda granar med födosöksspår runtom.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3435,10 +3467,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124806603</v>
+        <v>124802330</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
+        <v>88512</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,52 +3479,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437790</v>
+        <v>437866</v>
       </c>
       <c r="R25" t="n">
-        <v>7028422</v>
+        <v>7028363</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3524,7 +3542,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3534,12 +3552,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3692,10 +3710,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124801643</v>
+        <v>124807390</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3708,46 +3726,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437865</v>
+        <v>437771</v>
       </c>
       <c r="R27" t="n">
-        <v>7028458</v>
+        <v>7028497</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3776,7 +3785,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3786,12 +3795,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal fuktig granskog</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3818,10 +3827,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802342</v>
+        <v>124802109</v>
       </c>
       <c r="B28" t="n">
-        <v>75025</v>
+        <v>96395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3830,25 +3839,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3858,10 +3867,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437861</v>
+        <v>437857</v>
       </c>
       <c r="R28" t="n">
-        <v>7028347</v>
+        <v>7028393</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3893,7 +3902,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3903,12 +3912,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av död gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3935,10 +3944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124801717</v>
+        <v>124802401</v>
       </c>
       <c r="B29" t="n">
-        <v>75025</v>
+        <v>91166</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3951,21 +3960,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3975,10 +3984,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437880</v>
+        <v>437856</v>
       </c>
       <c r="R29" t="n">
-        <v>7028440</v>
+        <v>7028363</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4010,7 +4019,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4020,12 +4029,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog på fuktig mark</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4052,10 +4061,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124802182</v>
+        <v>124807162</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
+        <v>77889</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4068,43 +4077,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>437853</v>
+        <v>437731</v>
       </c>
       <c r="R30" t="n">
-        <v>7028377</v>
+        <v>7028449</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog i nordsluttning</t>
+          <t>På bark på undersidan av död gren på gammal levande gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124802848</v>
+        <v>124807102</v>
       </c>
       <c r="B31" t="n">
-        <v>91166</v>
+        <v>91162</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4194,21 +4194,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437865</v>
+        <v>437750</v>
       </c>
       <c r="R31" t="n">
-        <v>7028297</v>
+        <v>7028464</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På grov död gran i gammal fuktig granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124806603</v>
+        <v>124801891</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>79028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,40 +1038,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437790</v>
+        <v>437896</v>
       </c>
       <c r="R5" t="n">
-        <v>7028422</v>
+        <v>7028421</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
+          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124801891</v>
+        <v>124806603</v>
       </c>
       <c r="B6" t="n">
-        <v>79028</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,40 +1169,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437896</v>
+        <v>437790</v>
       </c>
       <c r="R6" t="n">
-        <v>7028421</v>
+        <v>7028422</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tunna levande kvistar på klen men gammal gran i gammal granskog på fuktig mark i nordsluttning</t>
+          <t>74 plantor och 5 vinterståndare på marken i gammal granskog med vitmossa, fuktig mark</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -3467,10 +3467,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802330</v>
+        <v>124802526</v>
       </c>
       <c r="B25" t="n">
-        <v>88512</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3483,34 +3483,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437866</v>
+        <v>437884</v>
       </c>
       <c r="R25" t="n">
-        <v>7028363</v>
+        <v>7028332</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3542,7 +3551,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3552,12 +3561,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
+          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3584,10 +3593,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802526</v>
+        <v>124802330</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>88512</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,43 +3609,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vargstugubrännan, Vargstugubrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437884</v>
+        <v>437866</v>
       </c>
       <c r="R26" t="n">
-        <v>7028332</v>
+        <v>7028363</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog (längsta bål 40 cm)</t>
+          <t>På gammal död gran (12 cm dbh, ca 150 år gammal) i gammal granskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -3348,7 +3348,7 @@
         <v>124804958</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -3348,7 +3348,7 @@
         <v>124804958</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30145-2021 artfynd.xlsx
+++ b/artfynd/A 30145-2021 artfynd.xlsx
@@ -3348,7 +3348,7 @@
         <v>124804958</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
